--- a/data/2026-05-02/BallparkPal_Teams.xlsx
+++ b/data/2026-05-02/BallparkPal_Teams.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="82">
   <si>
     <t>GamePk</t>
   </si>
@@ -176,6 +176,12 @@
     <t>WAS</t>
   </si>
   <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
     <t>LAD</t>
   </si>
   <si>
@@ -200,6 +206,12 @@
     <t>PIT</t>
   </si>
   <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
     <t>TOR</t>
   </si>
   <si>
@@ -222,6 +234,12 @@
   </si>
   <si>
     <t>DET</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>COL</t>
   </si>
   <si>
     <t>ARI</t>
@@ -582,7 +600,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AW25"/>
+  <dimension ref="A1:AW31"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:49">
@@ -751,141 +769,141 @@
         <v>52</v>
       </c>
       <c r="F2">
-        <v>4.6</v>
+        <v>4.548</v>
       </c>
       <c r="G2">
-        <v>0.536</v>
+        <v>0.507</v>
       </c>
       <c r="H2">
-        <v>0.101</v>
+        <v>0.091</v>
       </c>
       <c r="I2">
-        <v>0.297</v>
+        <v>0.286</v>
       </c>
       <c r="J2">
-        <v>0.09</v>
+        <v>0.099</v>
       </c>
       <c r="K2">
-        <v>0.208</v>
+        <v>0.223</v>
       </c>
       <c r="L2">
-        <v>0.812</v>
+        <v>0.747</v>
       </c>
       <c r="M2">
-        <v>0.115</v>
+        <v>0.129</v>
       </c>
       <c r="N2">
-        <v>1.651</v>
+        <v>1.797</v>
       </c>
       <c r="O2">
-        <v>6.064</v>
+        <v>5.879</v>
       </c>
       <c r="P2">
-        <v>4.032</v>
+        <v>3.931</v>
       </c>
       <c r="Q2">
-        <v>8.361</v>
+        <v>8.401</v>
       </c>
       <c r="R2">
-        <v>0.436</v>
+        <v>0.481</v>
       </c>
       <c r="S2">
-        <v>0.369</v>
+        <v>0.343</v>
       </c>
       <c r="T2">
-        <v>0.154</v>
+        <v>0.133</v>
       </c>
       <c r="U2">
-        <v>0.031</v>
+        <v>0.034</v>
       </c>
       <c r="V2">
-        <v>0.009</v>
+        <v>0.007</v>
       </c>
       <c r="W2">
         <v>0.001</v>
       </c>
       <c r="X2">
-        <v>0.056</v>
+        <v>0.061</v>
       </c>
       <c r="Y2">
-        <v>0.101</v>
+        <v>0.097</v>
       </c>
       <c r="Z2">
-        <v>0.125</v>
+        <v>0.123</v>
       </c>
       <c r="AA2">
-        <v>0.131</v>
+        <v>0.138</v>
       </c>
       <c r="AB2">
-        <v>0.127</v>
+        <v>0.132</v>
       </c>
       <c r="AC2">
-        <v>0.117</v>
+        <v>0.118</v>
       </c>
       <c r="AD2">
-        <v>0.091</v>
+        <v>0.099</v>
       </c>
       <c r="AE2">
-        <v>0.086</v>
+        <v>0.073</v>
       </c>
       <c r="AF2">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="AG2">
-        <v>0.042</v>
+        <v>0.039</v>
       </c>
       <c r="AH2">
-        <v>0.029</v>
+        <v>0.022</v>
       </c>
       <c r="AI2">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="AJ2">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="AK2">
-        <v>0.006</v>
+        <v>0.009</v>
       </c>
       <c r="AL2">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AM2">
         <v>0.005</v>
       </c>
       <c r="AN2">
-        <v>0.525</v>
+        <v>0.518</v>
       </c>
       <c r="AO2">
-        <v>0.403</v>
+        <v>0.424</v>
       </c>
       <c r="AP2">
+        <v>0.472</v>
+      </c>
+      <c r="AQ2">
+        <v>0.48</v>
+      </c>
+      <c r="AR2">
         <v>0.479</v>
       </c>
-      <c r="AQ2">
-        <v>0.51</v>
-      </c>
-      <c r="AR2">
-        <v>0.475</v>
-      </c>
       <c r="AS2">
-        <v>0.467</v>
+        <v>0.501</v>
       </c>
       <c r="AT2">
-        <v>0.473</v>
+        <v>0.442</v>
       </c>
       <c r="AU2">
-        <v>0.488</v>
+        <v>0.474</v>
       </c>
       <c r="AV2">
-        <v>0.471</v>
+        <v>0.461</v>
       </c>
       <c r="AW2">
-        <v>0.178</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="3" spans="1:49">
       <c r="A3">
-        <v>823067</v>
+        <v>822988</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -900,141 +918,141 @@
         <v>54</v>
       </c>
       <c r="F3">
-        <v>4.562</v>
+        <v>4.771</v>
       </c>
       <c r="G3">
-        <v>0.561</v>
+        <v>0.562</v>
       </c>
       <c r="H3">
-        <v>0.112</v>
+        <v>0.104</v>
       </c>
       <c r="I3">
-        <v>0.316</v>
+        <v>0.33</v>
       </c>
       <c r="J3">
-        <v>0.092</v>
+        <v>0.089</v>
       </c>
       <c r="K3">
-        <v>0.181</v>
+        <v>0.186</v>
       </c>
       <c r="L3">
-        <v>0.935</v>
+        <v>1.165</v>
       </c>
       <c r="M3">
-        <v>0.13</v>
+        <v>0.128</v>
       </c>
       <c r="N3">
-        <v>1.653</v>
+        <v>1.61</v>
       </c>
       <c r="O3">
-        <v>5.768</v>
+        <v>5.951</v>
       </c>
       <c r="P3">
-        <v>3.669</v>
+        <v>3.515</v>
       </c>
       <c r="Q3">
-        <v>6.743</v>
+        <v>8.626</v>
       </c>
       <c r="R3">
-        <v>0.385</v>
+        <v>0.315</v>
       </c>
       <c r="S3">
-        <v>0.379</v>
+        <v>0.37</v>
       </c>
       <c r="T3">
-        <v>0.171</v>
+        <v>0.197</v>
       </c>
       <c r="U3">
-        <v>0.048</v>
+        <v>0.084</v>
       </c>
       <c r="V3">
-        <v>0.013</v>
+        <v>0.027</v>
       </c>
       <c r="W3">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="X3">
-        <v>0.056</v>
+        <v>0.049</v>
       </c>
       <c r="Y3">
-        <v>0.092</v>
+        <v>0.09</v>
       </c>
       <c r="Z3">
-        <v>0.133</v>
+        <v>0.115</v>
       </c>
       <c r="AA3">
-        <v>0.135</v>
+        <v>0.119</v>
       </c>
       <c r="AB3">
-        <v>0.128</v>
+        <v>0.141</v>
       </c>
       <c r="AC3">
-        <v>0.113</v>
+        <v>0.123</v>
       </c>
       <c r="AD3">
-        <v>0.105</v>
+        <v>0.099</v>
       </c>
       <c r="AE3">
-        <v>0.08</v>
+        <v>0.083</v>
       </c>
       <c r="AF3">
-        <v>0.05</v>
+        <v>0.065</v>
       </c>
       <c r="AG3">
         <v>0.045</v>
       </c>
       <c r="AH3">
-        <v>0.024</v>
+        <v>0.03</v>
       </c>
       <c r="AI3">
         <v>0.017</v>
       </c>
       <c r="AJ3">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AK3">
+        <v>0.008</v>
+      </c>
+      <c r="AL3">
+        <v>0.003</v>
+      </c>
+      <c r="AM3">
         <v>0.006</v>
       </c>
-      <c r="AL3">
-        <v>0.004</v>
-      </c>
-      <c r="AM3">
-        <v>0.003</v>
-      </c>
       <c r="AN3">
-        <v>0.545</v>
+        <v>0.432</v>
       </c>
       <c r="AO3">
-        <v>0.456</v>
+        <v>0.469</v>
       </c>
       <c r="AP3">
+        <v>0.499</v>
+      </c>
+      <c r="AQ3">
+        <v>0.582</v>
+      </c>
+      <c r="AR3">
+        <v>0.544</v>
+      </c>
+      <c r="AS3">
+        <v>0.541</v>
+      </c>
+      <c r="AT3">
         <v>0.469</v>
       </c>
-      <c r="AQ3">
-        <v>0.461</v>
-      </c>
-      <c r="AR3">
-        <v>0.482</v>
-      </c>
-      <c r="AS3">
-        <v>0.468</v>
-      </c>
-      <c r="AT3">
-        <v>0.48</v>
-      </c>
       <c r="AU3">
-        <v>0.458</v>
+        <v>0.487</v>
       </c>
       <c r="AV3">
-        <v>0.457</v>
+        <v>0.473</v>
       </c>
       <c r="AW3">
-        <v>0.161</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="4" spans="1:49">
       <c r="A4">
-        <v>823144</v>
+        <v>823067</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -1049,141 +1067,141 @@
         <v>56</v>
       </c>
       <c r="F4">
-        <v>3.641</v>
+        <v>4.982</v>
       </c>
       <c r="G4">
-        <v>0.378</v>
+        <v>0.57</v>
       </c>
       <c r="H4">
-        <v>0.078</v>
+        <v>0.11</v>
       </c>
       <c r="I4">
-        <v>0.174</v>
+        <v>0.339</v>
       </c>
       <c r="J4">
-        <v>0.126</v>
+        <v>0.093</v>
       </c>
       <c r="K4">
-        <v>0.311</v>
+        <v>0.187</v>
       </c>
       <c r="L4">
-        <v>1.014</v>
+        <v>1.108</v>
       </c>
       <c r="M4">
-        <v>0.125</v>
+        <v>0.128</v>
       </c>
       <c r="N4">
-        <v>1.277</v>
+        <v>1.673</v>
       </c>
       <c r="O4">
-        <v>4.883</v>
+        <v>5.969</v>
       </c>
       <c r="P4">
-        <v>2.922</v>
+        <v>3.81</v>
       </c>
       <c r="Q4">
-        <v>8.291</v>
+        <v>6.651</v>
       </c>
       <c r="R4">
-        <v>0.367</v>
+        <v>0.336</v>
       </c>
       <c r="S4">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="T4">
-        <v>0.184</v>
+        <v>0.196</v>
       </c>
       <c r="U4">
-        <v>0.061</v>
+        <v>0.077</v>
       </c>
       <c r="V4">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="W4">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="X4">
-        <v>0.093</v>
+        <v>0.034</v>
       </c>
       <c r="Y4">
+        <v>0.086</v>
+      </c>
+      <c r="Z4">
+        <v>0.119</v>
+      </c>
+      <c r="AA4">
+        <v>0.121</v>
+      </c>
+      <c r="AB4">
         <v>0.132</v>
       </c>
-      <c r="Z4">
-        <v>0.165</v>
-      </c>
-      <c r="AA4">
-        <v>0.159</v>
-      </c>
-      <c r="AB4">
-        <v>0.13</v>
-      </c>
       <c r="AC4">
-        <v>0.104</v>
+        <v>0.131</v>
       </c>
       <c r="AD4">
-        <v>0.077</v>
+        <v>0.099</v>
       </c>
       <c r="AE4">
-        <v>0.052</v>
+        <v>0.088</v>
       </c>
       <c r="AF4">
-        <v>0.032</v>
+        <v>0.06</v>
       </c>
       <c r="AG4">
-        <v>0.026</v>
+        <v>0.046</v>
       </c>
       <c r="AH4">
-        <v>0.013</v>
+        <v>0.03</v>
       </c>
       <c r="AI4">
-        <v>0.007</v>
+        <v>0.02</v>
       </c>
       <c r="AJ4">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="AK4">
-        <v>0.002</v>
+        <v>0.009</v>
       </c>
       <c r="AL4">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="AM4">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="AN4">
-        <v>0.422</v>
+        <v>0.548</v>
       </c>
       <c r="AO4">
-        <v>0.371</v>
+        <v>0.507</v>
       </c>
       <c r="AP4">
-        <v>0.404</v>
+        <v>0.504</v>
       </c>
       <c r="AQ4">
-        <v>0.411</v>
+        <v>0.499</v>
       </c>
       <c r="AR4">
-        <v>0.351</v>
+        <v>0.518</v>
       </c>
       <c r="AS4">
-        <v>0.368</v>
+        <v>0.528</v>
       </c>
       <c r="AT4">
-        <v>0.381</v>
+        <v>0.536</v>
       </c>
       <c r="AU4">
-        <v>0.357</v>
+        <v>0.51</v>
       </c>
       <c r="AV4">
-        <v>0.374</v>
+        <v>0.529</v>
       </c>
       <c r="AW4">
-        <v>0.122</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="5" spans="1:49">
       <c r="A5">
-        <v>823308</v>
+        <v>823144</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
@@ -1198,141 +1216,141 @@
         <v>58</v>
       </c>
       <c r="F5">
-        <v>4.094</v>
+        <v>3.93</v>
       </c>
       <c r="G5">
-        <v>0.39</v>
+        <v>0.388</v>
       </c>
       <c r="H5">
-        <v>0.09</v>
+        <v>0.079</v>
       </c>
       <c r="I5">
-        <v>0.196</v>
+        <v>0.19</v>
       </c>
       <c r="J5">
+        <v>0.115</v>
+      </c>
+      <c r="K5">
+        <v>0.316</v>
+      </c>
+      <c r="L5">
+        <v>1.071</v>
+      </c>
+      <c r="M5">
+        <v>0.143</v>
+      </c>
+      <c r="N5">
+        <v>1.403</v>
+      </c>
+      <c r="O5">
+        <v>5.019</v>
+      </c>
+      <c r="P5">
+        <v>2.996</v>
+      </c>
+      <c r="Q5">
+        <v>8.505</v>
+      </c>
+      <c r="R5">
+        <v>0.348</v>
+      </c>
+      <c r="S5">
+        <v>0.358</v>
+      </c>
+      <c r="T5">
+        <v>0.197</v>
+      </c>
+      <c r="U5">
+        <v>0.074</v>
+      </c>
+      <c r="V5">
+        <v>0.019</v>
+      </c>
+      <c r="W5">
+        <v>0.004</v>
+      </c>
+      <c r="X5">
+        <v>0.077</v>
+      </c>
+      <c r="Y5">
+        <v>0.128</v>
+      </c>
+      <c r="Z5">
+        <v>0.141</v>
+      </c>
+      <c r="AA5">
+        <v>0.147</v>
+      </c>
+      <c r="AB5">
+        <v>0.138</v>
+      </c>
+      <c r="AC5">
         <v>0.117</v>
       </c>
-      <c r="K5">
-        <v>0.327</v>
-      </c>
-      <c r="L5">
-        <v>1.029</v>
-      </c>
-      <c r="M5">
-        <v>0.066</v>
-      </c>
-      <c r="N5">
-        <v>1.314</v>
-      </c>
-      <c r="O5">
-        <v>4.758</v>
-      </c>
-      <c r="P5">
-        <v>4.443</v>
-      </c>
-      <c r="Q5">
-        <v>9.333</v>
-      </c>
-      <c r="R5">
-        <v>0.354</v>
-      </c>
-      <c r="S5">
-        <v>0.374</v>
-      </c>
-      <c r="T5">
-        <v>0.189</v>
-      </c>
-      <c r="U5">
-        <v>0.062</v>
-      </c>
-      <c r="V5">
-        <v>0.015</v>
-      </c>
-      <c r="W5">
-        <v>0.006</v>
-      </c>
-      <c r="X5">
-        <v>0.066</v>
-      </c>
-      <c r="Y5">
-        <v>0.121</v>
-      </c>
-      <c r="Z5">
-        <v>0.147</v>
-      </c>
-      <c r="AA5">
-        <v>0.146</v>
-      </c>
-      <c r="AB5">
-        <v>0.135</v>
-      </c>
-      <c r="AC5">
-        <v>0.108</v>
-      </c>
       <c r="AD5">
-        <v>0.089</v>
+        <v>0.088</v>
       </c>
       <c r="AE5">
-        <v>0.071</v>
+        <v>0.058</v>
       </c>
       <c r="AF5">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
       <c r="AG5">
         <v>0.03</v>
       </c>
       <c r="AH5">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="AI5">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="AJ5">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AK5">
         <v>0.003</v>
       </c>
       <c r="AL5">
-        <v>0.0</v>
+        <v>0.003</v>
       </c>
       <c r="AM5">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AN5">
-        <v>0.506</v>
+        <v>0.476</v>
       </c>
       <c r="AO5">
-        <v>0.44</v>
+        <v>0.402</v>
       </c>
       <c r="AP5">
-        <v>0.459</v>
+        <v>0.441</v>
       </c>
       <c r="AQ5">
-        <v>0.444</v>
+        <v>0.416</v>
       </c>
       <c r="AR5">
-        <v>0.464</v>
+        <v>0.408</v>
       </c>
       <c r="AS5">
-        <v>0.414</v>
+        <v>0.388</v>
       </c>
       <c r="AT5">
-        <v>0.364</v>
+        <v>0.377</v>
       </c>
       <c r="AU5">
-        <v>0.394</v>
+        <v>0.411</v>
       </c>
       <c r="AV5">
-        <v>0.385</v>
+        <v>0.393</v>
       </c>
       <c r="AW5">
-        <v>0.122</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="6" spans="1:49">
       <c r="A6">
-        <v>823388</v>
+        <v>823308</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -1347,141 +1365,141 @@
         <v>60</v>
       </c>
       <c r="F6">
-        <v>3.965</v>
+        <v>4.133</v>
       </c>
       <c r="G6">
-        <v>0.386</v>
+        <v>0.362</v>
       </c>
       <c r="H6">
-        <v>0.089</v>
+        <v>0.076</v>
       </c>
       <c r="I6">
-        <v>0.194</v>
+        <v>0.177</v>
       </c>
       <c r="J6">
+        <v>0.12</v>
+      </c>
+      <c r="K6">
+        <v>0.333</v>
+      </c>
+      <c r="L6">
+        <v>1.069</v>
+      </c>
+      <c r="M6">
+        <v>0.063</v>
+      </c>
+      <c r="N6">
+        <v>1.331</v>
+      </c>
+      <c r="O6">
+        <v>4.689</v>
+      </c>
+      <c r="P6">
+        <v>4.398</v>
+      </c>
+      <c r="Q6">
+        <v>9.632</v>
+      </c>
+      <c r="R6">
+        <v>0.338</v>
+      </c>
+      <c r="S6">
+        <v>0.375</v>
+      </c>
+      <c r="T6">
+        <v>0.197</v>
+      </c>
+      <c r="U6">
+        <v>0.067</v>
+      </c>
+      <c r="V6">
+        <v>0.017</v>
+      </c>
+      <c r="W6">
+        <v>0.006</v>
+      </c>
+      <c r="X6">
+        <v>0.066</v>
+      </c>
+      <c r="Y6">
+        <v>0.114</v>
+      </c>
+      <c r="Z6">
+        <v>0.146</v>
+      </c>
+      <c r="AA6">
+        <v>0.141</v>
+      </c>
+      <c r="AB6">
+        <v>0.142</v>
+      </c>
+      <c r="AC6">
         <v>0.113</v>
       </c>
-      <c r="K6">
-        <v>0.316</v>
-      </c>
-      <c r="L6">
-        <v>0.775</v>
-      </c>
-      <c r="M6">
-        <v>0.173</v>
-      </c>
-      <c r="N6">
-        <v>1.514</v>
-      </c>
-      <c r="O6">
-        <v>5.11</v>
-      </c>
-      <c r="P6">
-        <v>4.016</v>
-      </c>
-      <c r="Q6">
-        <v>9.95</v>
-      </c>
-      <c r="R6">
-        <v>0.462</v>
-      </c>
-      <c r="S6">
-        <v>0.358</v>
-      </c>
-      <c r="T6">
-        <v>0.135</v>
-      </c>
-      <c r="U6">
-        <v>0.036</v>
-      </c>
-      <c r="V6">
-        <v>0.007</v>
-      </c>
-      <c r="W6">
-        <v>0.002</v>
-      </c>
-      <c r="X6">
-        <v>0.09</v>
-      </c>
-      <c r="Y6">
-        <v>0.123</v>
-      </c>
-      <c r="Z6">
-        <v>0.145</v>
-      </c>
-      <c r="AA6">
-        <v>0.143</v>
-      </c>
-      <c r="AB6">
-        <v>0.12</v>
-      </c>
-      <c r="AC6">
-        <v>0.114</v>
-      </c>
       <c r="AD6">
-        <v>0.079</v>
+        <v>0.083</v>
       </c>
       <c r="AE6">
-        <v>0.075</v>
+        <v>0.069</v>
       </c>
       <c r="AF6">
-        <v>0.039</v>
+        <v>0.047</v>
       </c>
       <c r="AG6">
-        <v>0.028</v>
+        <v>0.032</v>
       </c>
       <c r="AH6">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="AI6">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="AJ6">
         <v>0.007</v>
       </c>
       <c r="AK6">
+        <v>0.004</v>
+      </c>
+      <c r="AL6">
         <v>0.003</v>
-      </c>
-      <c r="AL6">
-        <v>0.004</v>
       </c>
       <c r="AM6">
         <v>0.002</v>
       </c>
       <c r="AN6">
-        <v>0.421</v>
+        <v>0.52</v>
       </c>
       <c r="AO6">
-        <v>0.43</v>
+        <v>0.413</v>
       </c>
       <c r="AP6">
-        <v>0.388</v>
+        <v>0.469</v>
       </c>
       <c r="AQ6">
-        <v>0.413</v>
+        <v>0.46</v>
       </c>
       <c r="AR6">
-        <v>0.409</v>
+        <v>0.438</v>
       </c>
       <c r="AS6">
-        <v>0.424</v>
+        <v>0.415</v>
       </c>
       <c r="AT6">
-        <v>0.42</v>
+        <v>0.408</v>
       </c>
       <c r="AU6">
-        <v>0.425</v>
+        <v>0.419</v>
       </c>
       <c r="AV6">
-        <v>0.391</v>
+        <v>0.379</v>
       </c>
       <c r="AW6">
-        <v>0.134</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="7" spans="1:49">
       <c r="A7">
-        <v>823715</v>
+        <v>823388</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
@@ -1496,141 +1514,141 @@
         <v>62</v>
       </c>
       <c r="F7">
-        <v>4.321</v>
+        <v>4.124</v>
       </c>
       <c r="G7">
-        <v>0.459</v>
+        <v>0.39</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>0.088</v>
       </c>
       <c r="I7">
-        <v>0.232</v>
+        <v>0.2</v>
       </c>
       <c r="J7">
-        <v>0.104</v>
+        <v>0.107</v>
       </c>
       <c r="K7">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="L7">
-        <v>1.148</v>
+        <v>0.798</v>
       </c>
       <c r="M7">
-        <v>0.091</v>
+        <v>0.178</v>
       </c>
       <c r="N7">
-        <v>1.571</v>
+        <v>1.507</v>
       </c>
       <c r="O7">
-        <v>5.051</v>
+        <v>5.264</v>
       </c>
       <c r="P7">
-        <v>3.614</v>
+        <v>4.117</v>
       </c>
       <c r="Q7">
-        <v>8.386</v>
+        <v>10.042</v>
       </c>
       <c r="R7">
-        <v>0.326</v>
+        <v>0.465</v>
       </c>
       <c r="S7">
-        <v>0.355</v>
+        <v>0.341</v>
       </c>
       <c r="T7">
-        <v>0.206</v>
+        <v>0.14</v>
       </c>
       <c r="U7">
-        <v>0.082</v>
+        <v>0.042</v>
       </c>
       <c r="V7">
-        <v>0.023</v>
+        <v>0.009</v>
       </c>
       <c r="W7">
-        <v>0.009</v>
+        <v>0.003</v>
       </c>
       <c r="X7">
+        <v>0.077</v>
+      </c>
+      <c r="Y7">
+        <v>0.129</v>
+      </c>
+      <c r="Z7">
+        <v>0.14</v>
+      </c>
+      <c r="AA7">
+        <v>0.126</v>
+      </c>
+      <c r="AB7">
+        <v>0.133</v>
+      </c>
+      <c r="AC7">
+        <v>0.115</v>
+      </c>
+      <c r="AD7">
+        <v>0.08</v>
+      </c>
+      <c r="AE7">
         <v>0.068</v>
       </c>
-      <c r="Y7">
-        <v>0.104</v>
-      </c>
-      <c r="Z7">
-        <v>0.139</v>
-      </c>
-      <c r="AA7">
-        <v>0.135</v>
-      </c>
-      <c r="AB7">
-        <v>0.141</v>
-      </c>
-      <c r="AC7">
-        <v>0.11</v>
-      </c>
-      <c r="AD7">
-        <v>0.089</v>
-      </c>
-      <c r="AE7">
-        <v>0.073</v>
-      </c>
       <c r="AF7">
-        <v>0.051</v>
+        <v>0.042</v>
       </c>
       <c r="AG7">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="AH7">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AI7">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="AJ7">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="AK7">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="AL7">
+        <v>0.003</v>
+      </c>
+      <c r="AM7">
         <v>0.004</v>
       </c>
-      <c r="AM7">
-        <v>0.005</v>
-      </c>
       <c r="AN7">
+        <v>0.399</v>
+      </c>
+      <c r="AO7">
+        <v>0.439</v>
+      </c>
+      <c r="AP7">
+        <v>0.405</v>
+      </c>
+      <c r="AQ7">
+        <v>0.436</v>
+      </c>
+      <c r="AR7">
+        <v>0.416</v>
+      </c>
+      <c r="AS7">
+        <v>0.455</v>
+      </c>
+      <c r="AT7">
+        <v>0.454</v>
+      </c>
+      <c r="AU7">
+        <v>0.45</v>
+      </c>
+      <c r="AV7">
         <v>0.442</v>
       </c>
-      <c r="AO7">
-        <v>0.396</v>
-      </c>
-      <c r="AP7">
-        <v>0.419</v>
-      </c>
-      <c r="AQ7">
-        <v>0.417</v>
-      </c>
-      <c r="AR7">
-        <v>0.428</v>
-      </c>
-      <c r="AS7">
-        <v>0.494</v>
-      </c>
-      <c r="AT7">
-        <v>0.475</v>
-      </c>
-      <c r="AU7">
-        <v>0.488</v>
-      </c>
-      <c r="AV7">
-        <v>0.519</v>
-      </c>
       <c r="AW7">
-        <v>0.15</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="8" spans="1:49">
       <c r="A8">
-        <v>823876</v>
+        <v>823554</v>
       </c>
       <c r="B8" t="s">
         <v>49</v>
@@ -1645,141 +1663,141 @@
         <v>64</v>
       </c>
       <c r="F8">
-        <v>4.403</v>
+        <v>4.507</v>
       </c>
       <c r="G8">
-        <v>0.534</v>
+        <v>0.427</v>
       </c>
       <c r="H8">
-        <v>0.114</v>
+        <v>0.081</v>
       </c>
       <c r="I8">
-        <v>0.286</v>
+        <v>0.242</v>
       </c>
       <c r="J8">
-        <v>0.092</v>
+        <v>0.11</v>
       </c>
       <c r="K8">
-        <v>0.197</v>
+        <v>0.285</v>
       </c>
       <c r="L8">
-        <v>0.887</v>
+        <v>1.164</v>
       </c>
       <c r="M8">
-        <v>0.123</v>
+        <v>0.095</v>
       </c>
       <c r="N8">
-        <v>1.71</v>
+        <v>1.452</v>
       </c>
       <c r="O8">
-        <v>5.455</v>
+        <v>5.78</v>
       </c>
       <c r="P8">
-        <v>3.638</v>
+        <v>3.527</v>
       </c>
       <c r="Q8">
-        <v>7.794</v>
+        <v>10.056</v>
       </c>
       <c r="R8">
-        <v>0.412</v>
+        <v>0.333</v>
       </c>
       <c r="S8">
-        <v>0.372</v>
+        <v>0.34</v>
       </c>
       <c r="T8">
-        <v>0.15</v>
+        <v>0.208</v>
       </c>
       <c r="U8">
-        <v>0.053</v>
+        <v>0.08</v>
       </c>
       <c r="V8">
-        <v>0.01</v>
+        <v>0.029</v>
       </c>
       <c r="W8">
-        <v>0.003</v>
+        <v>0.009</v>
       </c>
       <c r="X8">
-        <v>0.058</v>
+        <v>0.067</v>
       </c>
       <c r="Y8">
-        <v>0.099</v>
+        <v>0.101</v>
       </c>
       <c r="Z8">
-        <v>0.134</v>
+        <v>0.115</v>
       </c>
       <c r="AA8">
-        <v>0.14</v>
+        <v>0.138</v>
       </c>
       <c r="AB8">
         <v>0.132</v>
       </c>
       <c r="AC8">
-        <v>0.126</v>
+        <v>0.122</v>
       </c>
       <c r="AD8">
-        <v>0.098</v>
+        <v>0.086</v>
       </c>
       <c r="AE8">
-        <v>0.069</v>
+        <v>0.076</v>
       </c>
       <c r="AF8">
-        <v>0.049</v>
+        <v>0.053</v>
       </c>
       <c r="AG8">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="AH8">
         <v>0.026</v>
       </c>
       <c r="AI8">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="AJ8">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="AK8">
         <v>0.007</v>
       </c>
       <c r="AL8">
+        <v>0.006</v>
+      </c>
+      <c r="AM8">
         <v>0.002</v>
       </c>
-      <c r="AM8">
-        <v>0.003</v>
-      </c>
       <c r="AN8">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="AO8">
-        <v>0.458</v>
+        <v>0.462</v>
       </c>
       <c r="AP8">
-        <v>0.468</v>
+        <v>0.48</v>
       </c>
       <c r="AQ8">
+        <v>0.466</v>
+      </c>
+      <c r="AR8">
+        <v>0.485</v>
+      </c>
+      <c r="AS8">
         <v>0.454</v>
       </c>
-      <c r="AR8">
-        <v>0.433</v>
-      </c>
-      <c r="AS8">
-        <v>0.47</v>
-      </c>
       <c r="AT8">
-        <v>0.434</v>
+        <v>0.463</v>
       </c>
       <c r="AU8">
-        <v>0.435</v>
+        <v>0.48</v>
       </c>
       <c r="AV8">
-        <v>0.436</v>
+        <v>0.475</v>
       </c>
       <c r="AW8">
-        <v>0.156</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="9" spans="1:49">
       <c r="A9">
-        <v>824042</v>
+        <v>823715</v>
       </c>
       <c r="B9" t="s">
         <v>49</v>
@@ -1794,141 +1812,141 @@
         <v>66</v>
       </c>
       <c r="F9">
-        <v>4.349</v>
+        <v>4.222</v>
       </c>
       <c r="G9">
-        <v>0.517</v>
+        <v>0.43</v>
       </c>
       <c r="H9">
-        <v>0.11</v>
+        <v>0.083</v>
       </c>
       <c r="I9">
-        <v>0.288</v>
+        <v>0.22</v>
       </c>
       <c r="J9">
-        <v>0.108</v>
+        <v>0.104</v>
       </c>
       <c r="K9">
-        <v>0.196</v>
+        <v>0.285</v>
       </c>
       <c r="L9">
-        <v>1.228</v>
+        <v>1.071</v>
       </c>
       <c r="M9">
-        <v>0.092</v>
+        <v>0.086</v>
       </c>
       <c r="N9">
-        <v>1.491</v>
+        <v>1.553</v>
       </c>
       <c r="O9">
-        <v>5.254</v>
+        <v>5.177</v>
       </c>
       <c r="P9">
-        <v>3.33</v>
+        <v>3.486</v>
       </c>
       <c r="Q9">
-        <v>10.741</v>
+        <v>8.227</v>
       </c>
       <c r="R9">
-        <v>0.298</v>
+        <v>0.351</v>
       </c>
       <c r="S9">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="T9">
-        <v>0.214</v>
+        <v>0.194</v>
       </c>
       <c r="U9">
-        <v>0.095</v>
+        <v>0.074</v>
       </c>
       <c r="V9">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="W9">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="X9">
-        <v>0.066</v>
+        <v>0.069</v>
       </c>
       <c r="Y9">
-        <v>0.107</v>
+        <v>0.118</v>
       </c>
       <c r="Z9">
-        <v>0.123</v>
+        <v>0.135</v>
       </c>
       <c r="AA9">
-        <v>0.149</v>
+        <v>0.144</v>
       </c>
       <c r="AB9">
-        <v>0.132</v>
+        <v>0.125</v>
       </c>
       <c r="AC9">
         <v>0.113</v>
       </c>
       <c r="AD9">
-        <v>0.097</v>
+        <v>0.089</v>
       </c>
       <c r="AE9">
-        <v>0.069</v>
+        <v>0.063</v>
       </c>
       <c r="AF9">
-        <v>0.051</v>
+        <v>0.054</v>
       </c>
       <c r="AG9">
         <v>0.034</v>
       </c>
       <c r="AH9">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="AI9">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="AJ9">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
       <c r="AK9">
         <v>0.005</v>
       </c>
       <c r="AL9">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AM9">
         <v>0.003</v>
       </c>
       <c r="AN9">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="AO9">
-        <v>0.397</v>
+        <v>0.389</v>
       </c>
       <c r="AP9">
-        <v>0.426</v>
+        <v>0.416</v>
       </c>
       <c r="AQ9">
-        <v>0.397</v>
+        <v>0.436</v>
       </c>
       <c r="AR9">
-        <v>0.441</v>
+        <v>0.422</v>
       </c>
       <c r="AS9">
-        <v>0.475</v>
+        <v>0.466</v>
       </c>
       <c r="AT9">
-        <v>0.501</v>
+        <v>0.486</v>
       </c>
       <c r="AU9">
-        <v>0.516</v>
+        <v>0.493</v>
       </c>
       <c r="AV9">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="AW9">
-        <v>0.151</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="10" spans="1:49">
       <c r="A10">
-        <v>824284</v>
+        <v>823876</v>
       </c>
       <c r="B10" t="s">
         <v>49</v>
@@ -1943,141 +1961,141 @@
         <v>68</v>
       </c>
       <c r="F10">
-        <v>4.56</v>
+        <v>4.472</v>
       </c>
       <c r="G10">
-        <v>0.407</v>
+        <v>0.52</v>
       </c>
       <c r="H10">
-        <v>0.081</v>
+        <v>0.099</v>
       </c>
       <c r="I10">
-        <v>0.217</v>
+        <v>0.288</v>
       </c>
       <c r="J10">
+        <v>0.085</v>
+      </c>
+      <c r="K10">
+        <v>0.213</v>
+      </c>
+      <c r="L10">
+        <v>0.858</v>
+      </c>
+      <c r="M10">
+        <v>0.159</v>
+      </c>
+      <c r="N10">
+        <v>1.721</v>
+      </c>
+      <c r="O10">
+        <v>5.736</v>
+      </c>
+      <c r="P10">
+        <v>3.519</v>
+      </c>
+      <c r="Q10">
+        <v>7.683</v>
+      </c>
+      <c r="R10">
+        <v>0.429</v>
+      </c>
+      <c r="S10">
+        <v>0.354</v>
+      </c>
+      <c r="T10">
+        <v>0.159</v>
+      </c>
+      <c r="U10">
+        <v>0.048</v>
+      </c>
+      <c r="V10">
+        <v>0.007</v>
+      </c>
+      <c r="W10">
+        <v>0.002</v>
+      </c>
+      <c r="X10">
+        <v>0.061</v>
+      </c>
+      <c r="Y10">
+        <v>0.098</v>
+      </c>
+      <c r="Z10">
+        <v>0.129</v>
+      </c>
+      <c r="AA10">
+        <v>0.135</v>
+      </c>
+      <c r="AB10">
+        <v>0.134</v>
+      </c>
+      <c r="AC10">
+        <v>0.121</v>
+      </c>
+      <c r="AD10">
         <v>0.099</v>
       </c>
-      <c r="K10">
-        <v>0.318</v>
-      </c>
-      <c r="L10">
-        <v>0.839</v>
-      </c>
-      <c r="M10">
-        <v>0.135</v>
-      </c>
-      <c r="N10">
-        <v>1.915</v>
-      </c>
-      <c r="O10">
-        <v>5.749</v>
-      </c>
-      <c r="P10">
-        <v>3.384</v>
-      </c>
-      <c r="Q10">
-        <v>7.926</v>
-      </c>
-      <c r="R10">
-        <v>0.436</v>
-      </c>
-      <c r="S10">
-        <v>0.358</v>
-      </c>
-      <c r="T10">
-        <v>0.15</v>
-      </c>
-      <c r="U10">
-        <v>0.043</v>
-      </c>
-      <c r="V10">
-        <v>0.009</v>
-      </c>
-      <c r="W10">
-        <v>0.003</v>
-      </c>
-      <c r="X10">
-        <v>0.06</v>
-      </c>
-      <c r="Y10">
-        <v>0.102</v>
-      </c>
-      <c r="Z10">
-        <v>0.125</v>
-      </c>
-      <c r="AA10">
-        <v>0.137</v>
-      </c>
-      <c r="AB10">
-        <v>0.128</v>
-      </c>
-      <c r="AC10">
-        <v>0.117</v>
-      </c>
-      <c r="AD10">
-        <v>0.092</v>
-      </c>
       <c r="AE10">
-        <v>0.074</v>
+        <v>0.071</v>
       </c>
       <c r="AF10">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
       <c r="AG10">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="AH10">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="AI10">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="AJ10">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AK10">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AL10">
         <v>0.005</v>
       </c>
       <c r="AM10">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="AN10">
-        <v>0.497</v>
+        <v>0.543</v>
       </c>
       <c r="AO10">
-        <v>0.433</v>
+        <v>0.427</v>
       </c>
       <c r="AP10">
-        <v>0.447</v>
+        <v>0.493</v>
       </c>
       <c r="AQ10">
-        <v>0.456</v>
+        <v>0.452</v>
       </c>
       <c r="AR10">
-        <v>0.484</v>
+        <v>0.487</v>
       </c>
       <c r="AS10">
-        <v>0.487</v>
+        <v>0.442</v>
       </c>
       <c r="AT10">
-        <v>0.507</v>
+        <v>0.46</v>
       </c>
       <c r="AU10">
-        <v>0.508</v>
+        <v>0.422</v>
       </c>
       <c r="AV10">
-        <v>0.47</v>
+        <v>0.452</v>
       </c>
       <c r="AW10">
-        <v>0.136</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="11" spans="1:49">
       <c r="A11">
-        <v>824685</v>
+        <v>824042</v>
       </c>
       <c r="B11" t="s">
         <v>49</v>
@@ -2092,141 +2110,141 @@
         <v>70</v>
       </c>
       <c r="F11">
-        <v>3.997</v>
+        <v>4.554</v>
       </c>
       <c r="G11">
-        <v>0.409</v>
+        <v>0.519</v>
       </c>
       <c r="H11">
-        <v>0.087</v>
+        <v>0.089</v>
       </c>
       <c r="I11">
-        <v>0.203</v>
+        <v>0.3</v>
       </c>
       <c r="J11">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="K11">
-        <v>0.305</v>
+        <v>0.209</v>
       </c>
       <c r="L11">
-        <v>0.905</v>
+        <v>1.306</v>
       </c>
       <c r="M11">
-        <v>0.169</v>
+        <v>0.121</v>
       </c>
       <c r="N11">
-        <v>1.474</v>
+        <v>1.556</v>
       </c>
       <c r="O11">
-        <v>5.445</v>
+        <v>5.265</v>
       </c>
       <c r="P11">
-        <v>2.989</v>
+        <v>3.304</v>
       </c>
       <c r="Q11">
-        <v>7.689</v>
+        <v>10.645</v>
       </c>
       <c r="R11">
-        <v>0.41</v>
+        <v>0.288</v>
       </c>
       <c r="S11">
-        <v>0.357</v>
+        <v>0.342</v>
       </c>
       <c r="T11">
-        <v>0.168</v>
+        <v>0.222</v>
       </c>
       <c r="U11">
-        <v>0.051</v>
+        <v>0.093</v>
       </c>
       <c r="V11">
-        <v>0.013</v>
+        <v>0.038</v>
       </c>
       <c r="W11">
-        <v>0.001</v>
+        <v>0.016</v>
       </c>
       <c r="X11">
-        <v>0.081</v>
+        <v>0.065</v>
       </c>
       <c r="Y11">
-        <v>0.13</v>
+        <v>0.097</v>
       </c>
       <c r="Z11">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="AA11">
-        <v>0.148</v>
+        <v>0.138</v>
       </c>
       <c r="AB11">
-        <v>0.131</v>
+        <v>0.122</v>
       </c>
       <c r="AC11">
-        <v>0.114</v>
+        <v>0.118</v>
       </c>
       <c r="AD11">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="AE11">
-        <v>0.061</v>
+        <v>0.083</v>
       </c>
       <c r="AF11">
-        <v>0.041</v>
+        <v>0.057</v>
       </c>
       <c r="AG11">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="AH11">
-        <v>0.019</v>
+        <v>0.027</v>
       </c>
       <c r="AI11">
+        <v>0.017</v>
+      </c>
+      <c r="AJ11">
         <v>0.012</v>
       </c>
-      <c r="AJ11">
-        <v>0.006</v>
-      </c>
       <c r="AK11">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="AL11">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AM11">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="AN11">
-        <v>0.439</v>
+        <v>0.477</v>
       </c>
       <c r="AO11">
-        <v>0.354</v>
+        <v>0.43</v>
       </c>
       <c r="AP11">
-        <v>0.415</v>
+        <v>0.441</v>
       </c>
       <c r="AQ11">
-        <v>0.366</v>
+        <v>0.435</v>
       </c>
       <c r="AR11">
-        <v>0.38</v>
+        <v>0.472</v>
       </c>
       <c r="AS11">
-        <v>0.427</v>
+        <v>0.501</v>
       </c>
       <c r="AT11">
-        <v>0.445</v>
+        <v>0.488</v>
       </c>
       <c r="AU11">
-        <v>0.441</v>
+        <v>0.529</v>
       </c>
       <c r="AV11">
-        <v>0.47</v>
+        <v>0.541</v>
       </c>
       <c r="AW11">
-        <v>0.161</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="12" spans="1:49">
       <c r="A12">
-        <v>824771</v>
+        <v>824284</v>
       </c>
       <c r="B12" t="s">
         <v>49</v>
@@ -2241,141 +2259,141 @@
         <v>72</v>
       </c>
       <c r="F12">
-        <v>4.982</v>
+        <v>4.504</v>
       </c>
       <c r="G12">
-        <v>0.425</v>
+        <v>0.394</v>
       </c>
       <c r="H12">
         <v>0.08</v>
       </c>
       <c r="I12">
-        <v>0.233</v>
+        <v>0.203</v>
       </c>
       <c r="J12">
-        <v>0.112</v>
+        <v>0.102</v>
       </c>
       <c r="K12">
-        <v>0.3</v>
+        <v>0.326</v>
       </c>
       <c r="L12">
-        <v>1.215</v>
+        <v>0.892</v>
       </c>
       <c r="M12">
-        <v>0.095</v>
+        <v>0.135</v>
       </c>
       <c r="N12">
-        <v>2.034</v>
+        <v>1.863</v>
       </c>
       <c r="O12">
-        <v>5.434</v>
+        <v>5.601</v>
       </c>
       <c r="P12">
-        <v>3.736</v>
+        <v>3.25</v>
       </c>
       <c r="Q12">
-        <v>8.056</v>
+        <v>7.923</v>
       </c>
       <c r="R12">
-        <v>0.303</v>
+        <v>0.409</v>
       </c>
       <c r="S12">
-        <v>0.366</v>
+        <v>0.371</v>
       </c>
       <c r="T12">
-        <v>0.199</v>
+        <v>0.156</v>
       </c>
       <c r="U12">
-        <v>0.09</v>
+        <v>0.049</v>
       </c>
       <c r="V12">
-        <v>0.033</v>
+        <v>0.013</v>
       </c>
       <c r="W12">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="X12">
-        <v>0.044</v>
+        <v>0.056</v>
       </c>
       <c r="Y12">
-        <v>0.087</v>
+        <v>0.104</v>
       </c>
       <c r="Z12">
-        <v>0.119</v>
+        <v>0.128</v>
       </c>
       <c r="AA12">
-        <v>0.127</v>
+        <v>0.137</v>
       </c>
       <c r="AB12">
-        <v>0.134</v>
+        <v>0.141</v>
       </c>
       <c r="AC12">
-        <v>0.109</v>
+        <v>0.106</v>
       </c>
       <c r="AD12">
-        <v>0.087</v>
+        <v>0.104</v>
       </c>
       <c r="AE12">
-        <v>0.085</v>
+        <v>0.065</v>
       </c>
       <c r="AF12">
-        <v>0.069</v>
+        <v>0.052</v>
       </c>
       <c r="AG12">
-        <v>0.046</v>
+        <v>0.041</v>
       </c>
       <c r="AH12">
-        <v>0.033</v>
+        <v>0.026</v>
       </c>
       <c r="AI12">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="AJ12">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="AK12">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="AL12">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="AM12">
-        <v>0.009</v>
+        <v>0.006</v>
       </c>
       <c r="AN12">
-        <v>0.601</v>
+        <v>0.459</v>
       </c>
       <c r="AO12">
+        <v>0.442</v>
+      </c>
+      <c r="AP12">
         <v>0.462</v>
       </c>
-      <c r="AP12">
-        <v>0.533</v>
-      </c>
       <c r="AQ12">
-        <v>0.488</v>
+        <v>0.462</v>
       </c>
       <c r="AR12">
-        <v>0.491</v>
+        <v>0.46</v>
       </c>
       <c r="AS12">
-        <v>0.559</v>
+        <v>0.49</v>
       </c>
       <c r="AT12">
-        <v>0.541</v>
+        <v>0.501</v>
       </c>
       <c r="AU12">
-        <v>0.529</v>
+        <v>0.506</v>
       </c>
       <c r="AV12">
-        <v>0.518</v>
+        <v>0.461</v>
       </c>
       <c r="AW12">
-        <v>0.144</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="13" spans="1:49">
       <c r="A13">
-        <v>825014</v>
+        <v>824365</v>
       </c>
       <c r="B13" t="s">
         <v>49</v>
@@ -2390,729 +2408,729 @@
         <v>74</v>
       </c>
       <c r="F13">
-        <v>5.117</v>
+        <v>6.16</v>
       </c>
       <c r="G13">
-        <v>0.373</v>
+        <v>0.595</v>
       </c>
       <c r="H13">
-        <v>0.074</v>
+        <v>0.1</v>
       </c>
       <c r="I13">
-        <v>0.209</v>
+        <v>0.389</v>
       </c>
       <c r="J13">
-        <v>0.097</v>
+        <v>0.085</v>
       </c>
       <c r="K13">
-        <v>0.376</v>
+        <v>0.177</v>
       </c>
       <c r="L13">
-        <v>1.32</v>
+        <v>1.626</v>
       </c>
       <c r="M13">
-        <v>0.114</v>
+        <v>0.124</v>
       </c>
       <c r="N13">
-        <v>1.941</v>
+        <v>1.817</v>
       </c>
       <c r="O13">
-        <v>5.214</v>
+        <v>6.026</v>
       </c>
       <c r="P13">
-        <v>4.084</v>
+        <v>4.301</v>
       </c>
       <c r="Q13">
-        <v>8.286</v>
+        <v>7.247</v>
       </c>
       <c r="R13">
-        <v>0.272</v>
+        <v>0.213</v>
       </c>
       <c r="S13">
-        <v>0.344</v>
+        <v>0.303</v>
       </c>
       <c r="T13">
-        <v>0.233</v>
+        <v>0.256</v>
       </c>
       <c r="U13">
-        <v>0.103</v>
+        <v>0.137</v>
       </c>
       <c r="V13">
-        <v>0.04</v>
+        <v>0.063</v>
       </c>
       <c r="W13">
-        <v>0.008</v>
+        <v>0.028</v>
       </c>
       <c r="X13">
-        <v>0.045</v>
+        <v>0.024</v>
       </c>
       <c r="Y13">
-        <v>0.083</v>
+        <v>0.052</v>
       </c>
       <c r="Z13">
-        <v>0.108</v>
+        <v>0.07</v>
       </c>
       <c r="AA13">
+        <v>0.1</v>
+      </c>
+      <c r="AB13">
         <v>0.122</v>
       </c>
-      <c r="AB13">
-        <v>0.123</v>
-      </c>
       <c r="AC13">
-        <v>0.114</v>
+        <v>0.115</v>
       </c>
       <c r="AD13">
         <v>0.106</v>
       </c>
       <c r="AE13">
-        <v>0.081</v>
+        <v>0.089</v>
       </c>
       <c r="AF13">
-        <v>0.063</v>
+        <v>0.077</v>
       </c>
       <c r="AG13">
-        <v>0.047</v>
+        <v>0.064</v>
       </c>
       <c r="AH13">
-        <v>0.032</v>
+        <v>0.061</v>
       </c>
       <c r="AI13">
-        <v>0.031</v>
+        <v>0.042</v>
       </c>
       <c r="AJ13">
-        <v>0.017</v>
+        <v>0.026</v>
       </c>
       <c r="AK13">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="AL13">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="AM13">
-        <v>0.011</v>
+        <v>0.024</v>
       </c>
       <c r="AN13">
-        <v>0.494</v>
+        <v>0.676</v>
       </c>
       <c r="AO13">
-        <v>0.507</v>
+        <v>0.547</v>
       </c>
       <c r="AP13">
-        <v>0.569</v>
+        <v>0.644</v>
       </c>
       <c r="AQ13">
-        <v>0.522</v>
+        <v>0.622</v>
       </c>
       <c r="AR13">
-        <v>0.544</v>
+        <v>0.648</v>
       </c>
       <c r="AS13">
-        <v>0.552</v>
+        <v>0.673</v>
       </c>
       <c r="AT13">
-        <v>0.545</v>
+        <v>0.686</v>
       </c>
       <c r="AU13">
-        <v>0.57</v>
+        <v>0.664</v>
       </c>
       <c r="AV13">
-        <v>0.587</v>
+        <v>0.717</v>
       </c>
       <c r="AW13">
-        <v>0.109</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="14" spans="1:49">
       <c r="A14">
-        <v>822746</v>
+        <v>824685</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
       </c>
       <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
         <v>75</v>
       </c>
-      <c r="D14" t="s">
-        <v>52</v>
-      </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="F14">
-        <v>4.117</v>
+        <v>3.997</v>
       </c>
       <c r="G14">
-        <v>0.464</v>
+        <v>0.413</v>
       </c>
       <c r="H14">
         <v>0.09</v>
       </c>
       <c r="I14">
-        <v>0.208</v>
+        <v>0.204</v>
       </c>
       <c r="J14">
-        <v>0.101</v>
+        <v>0.116</v>
       </c>
       <c r="K14">
-        <v>0.297</v>
+        <v>0.289</v>
       </c>
       <c r="L14">
-        <v>0.789</v>
+        <v>0.925</v>
       </c>
       <c r="M14">
-        <v>0.101</v>
+        <v>0.175</v>
       </c>
       <c r="N14">
-        <v>1.478</v>
+        <v>1.419</v>
       </c>
       <c r="O14">
-        <v>5.702</v>
+        <v>5.417</v>
       </c>
       <c r="P14">
-        <v>3.605</v>
+        <v>3.068</v>
       </c>
       <c r="Q14">
-        <v>9.753</v>
+        <v>7.351</v>
       </c>
       <c r="R14">
-        <v>0.444</v>
+        <v>0.404</v>
       </c>
       <c r="S14">
-        <v>0.375</v>
+        <v>0.358</v>
       </c>
       <c r="T14">
-        <v>0.137</v>
+        <v>0.168</v>
       </c>
       <c r="U14">
-        <v>0.035</v>
+        <v>0.054</v>
       </c>
       <c r="V14">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="W14">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="X14">
-        <v>0.058</v>
+        <v>0.084</v>
       </c>
       <c r="Y14">
-        <v>0.111</v>
+        <v>0.123</v>
       </c>
       <c r="Z14">
+        <v>0.139</v>
+      </c>
+      <c r="AA14">
         <v>0.146</v>
       </c>
-      <c r="AA14">
-        <v>0.161</v>
-      </c>
       <c r="AB14">
-        <v>0.135</v>
+        <v>0.129</v>
       </c>
       <c r="AC14">
-        <v>0.118</v>
+        <v>0.11</v>
       </c>
       <c r="AD14">
-        <v>0.091</v>
+        <v>0.088</v>
       </c>
       <c r="AE14">
-        <v>0.058</v>
+        <v>0.062</v>
       </c>
       <c r="AF14">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="AG14">
-        <v>0.029</v>
+        <v>0.034</v>
       </c>
       <c r="AH14">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="AI14">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="AJ14">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AK14">
         <v>0.004</v>
       </c>
       <c r="AL14">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AM14">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AN14">
-        <v>0.491</v>
+        <v>0.447</v>
       </c>
       <c r="AO14">
-        <v>0.507</v>
+        <v>0.355</v>
       </c>
       <c r="AP14">
+        <v>0.394</v>
+      </c>
+      <c r="AQ14">
+        <v>0.377</v>
+      </c>
+      <c r="AR14">
+        <v>0.407</v>
+      </c>
+      <c r="AS14">
+        <v>0.42</v>
+      </c>
+      <c r="AT14">
+        <v>0.432</v>
+      </c>
+      <c r="AU14">
         <v>0.465</v>
       </c>
-      <c r="AQ14">
-        <v>0.449</v>
-      </c>
-      <c r="AR14">
-        <v>0.436</v>
-      </c>
-      <c r="AS14">
-        <v>0.426</v>
-      </c>
-      <c r="AT14">
-        <v>0.425</v>
-      </c>
-      <c r="AU14">
-        <v>0.441</v>
-      </c>
       <c r="AV14">
-        <v>0.254</v>
+        <v>0.447</v>
       </c>
       <c r="AW14">
-        <v>0.123</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="15" spans="1:49">
       <c r="A15">
-        <v>823067</v>
+        <v>824771</v>
       </c>
       <c r="B15" t="s">
         <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F15">
-        <v>3.795</v>
+        <v>4.938</v>
       </c>
       <c r="G15">
-        <v>0.439</v>
+        <v>0.404</v>
       </c>
       <c r="H15">
-        <v>0.092</v>
+        <v>0.077</v>
       </c>
       <c r="I15">
-        <v>0.181</v>
+        <v>0.238</v>
       </c>
       <c r="J15">
-        <v>0.112</v>
+        <v>0.1</v>
       </c>
       <c r="K15">
+        <v>0.318</v>
+      </c>
+      <c r="L15">
+        <v>1.183</v>
+      </c>
+      <c r="M15">
+        <v>0.082</v>
+      </c>
+      <c r="N15">
+        <v>2.024</v>
+      </c>
+      <c r="O15">
+        <v>5.432</v>
+      </c>
+      <c r="P15">
+        <v>3.802</v>
+      </c>
+      <c r="Q15">
+        <v>7.973</v>
+      </c>
+      <c r="R15">
         <v>0.316</v>
-      </c>
-      <c r="L15">
-        <v>0.71</v>
-      </c>
-      <c r="M15">
-        <v>0.046</v>
-      </c>
-      <c r="N15">
-        <v>1.554</v>
-      </c>
-      <c r="O15">
-        <v>4.752</v>
-      </c>
-      <c r="P15">
-        <v>4.156</v>
-      </c>
-      <c r="Q15">
-        <v>8.015</v>
-      </c>
-      <c r="R15">
-        <v>0.489</v>
       </c>
       <c r="S15">
         <v>0.353</v>
       </c>
       <c r="T15">
-        <v>0.123</v>
+        <v>0.209</v>
       </c>
       <c r="U15">
-        <v>0.03</v>
+        <v>0.087</v>
       </c>
       <c r="V15">
-        <v>0.005</v>
+        <v>0.024</v>
       </c>
       <c r="W15">
-        <v>0.0</v>
+        <v>0.011</v>
       </c>
       <c r="X15">
-        <v>0.075</v>
+        <v>0.053</v>
       </c>
       <c r="Y15">
+        <v>0.091</v>
+      </c>
+      <c r="Z15">
         <v>0.12</v>
       </c>
-      <c r="Z15">
-        <v>0.149</v>
-      </c>
       <c r="AA15">
-        <v>0.176</v>
+        <v>0.129</v>
       </c>
       <c r="AB15">
-        <v>0.138</v>
+        <v>0.119</v>
       </c>
       <c r="AC15">
         <v>0.115</v>
       </c>
       <c r="AD15">
-        <v>0.078</v>
+        <v>0.091</v>
       </c>
       <c r="AE15">
-        <v>0.06</v>
+        <v>0.076</v>
       </c>
       <c r="AF15">
-        <v>0.038</v>
+        <v>0.061</v>
       </c>
       <c r="AG15">
-        <v>0.02</v>
+        <v>0.039</v>
       </c>
       <c r="AH15">
+        <v>0.034</v>
+      </c>
+      <c r="AI15">
+        <v>0.026</v>
+      </c>
+      <c r="AJ15">
+        <v>0.018</v>
+      </c>
+      <c r="AK15">
         <v>0.012</v>
       </c>
-      <c r="AI15">
-        <v>0.009</v>
-      </c>
-      <c r="AJ15">
-        <v>0.005</v>
-      </c>
-      <c r="AK15">
-        <v>0.002</v>
-      </c>
       <c r="AL15">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="AM15">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="AN15">
-        <v>0.495</v>
+        <v>0.574</v>
       </c>
       <c r="AO15">
-        <v>0.408</v>
+        <v>0.469</v>
       </c>
       <c r="AP15">
-        <v>0.49</v>
+        <v>0.506</v>
       </c>
       <c r="AQ15">
-        <v>0.417</v>
+        <v>0.489</v>
       </c>
       <c r="AR15">
-        <v>0.408</v>
+        <v>0.513</v>
       </c>
       <c r="AS15">
-        <v>0.374</v>
+        <v>0.532</v>
       </c>
       <c r="AT15">
-        <v>0.385</v>
+        <v>0.546</v>
       </c>
       <c r="AU15">
-        <v>0.371</v>
+        <v>0.554</v>
       </c>
       <c r="AV15">
-        <v>0.23</v>
+        <v>0.529</v>
       </c>
       <c r="AW15">
-        <v>0.12</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="16" spans="1:49">
       <c r="A16">
-        <v>823144</v>
+        <v>825014</v>
       </c>
       <c r="B16" t="s">
         <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F16">
-        <v>4.515</v>
+        <v>4.949</v>
       </c>
       <c r="G16">
-        <v>0.622</v>
+        <v>0.376</v>
       </c>
       <c r="H16">
-        <v>0.126</v>
+        <v>0.082</v>
       </c>
       <c r="I16">
-        <v>0.311</v>
+        <v>0.193</v>
       </c>
       <c r="J16">
-        <v>0.078</v>
+        <v>0.112</v>
       </c>
       <c r="K16">
-        <v>0.174</v>
+        <v>0.356</v>
       </c>
       <c r="L16">
-        <v>1.493</v>
+        <v>1.279</v>
       </c>
       <c r="M16">
-        <v>0.08</v>
+        <v>0.102</v>
       </c>
       <c r="N16">
-        <v>1.38</v>
+        <v>2.027</v>
       </c>
       <c r="O16">
-        <v>4.692</v>
+        <v>4.935</v>
       </c>
       <c r="P16">
-        <v>3.439</v>
+        <v>4.044</v>
       </c>
       <c r="Q16">
-        <v>8.32</v>
+        <v>8.335</v>
       </c>
       <c r="R16">
-        <v>0.214</v>
+        <v>0.287</v>
       </c>
       <c r="S16">
-        <v>0.348</v>
+        <v>0.357</v>
       </c>
       <c r="T16">
-        <v>0.253</v>
+        <v>0.213</v>
       </c>
       <c r="U16">
-        <v>0.123</v>
+        <v>0.092</v>
       </c>
       <c r="V16">
-        <v>0.044</v>
+        <v>0.035</v>
       </c>
       <c r="W16">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="X16">
-        <v>0.042</v>
+        <v>0.05</v>
       </c>
       <c r="Y16">
-        <v>0.084</v>
+        <v>0.086</v>
       </c>
       <c r="Z16">
-        <v>0.118</v>
+        <v>0.119</v>
       </c>
       <c r="AA16">
-        <v>0.15</v>
+        <v>0.121</v>
       </c>
       <c r="AB16">
-        <v>0.155</v>
+        <v>0.135</v>
       </c>
       <c r="AC16">
-        <v>0.14</v>
+        <v>0.112</v>
       </c>
       <c r="AD16">
-        <v>0.093</v>
+        <v>0.099</v>
       </c>
       <c r="AE16">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AF16">
-        <v>0.056</v>
+        <v>0.061</v>
       </c>
       <c r="AG16">
-        <v>0.037</v>
+        <v>0.045</v>
       </c>
       <c r="AH16">
-        <v>0.021</v>
+        <v>0.031</v>
       </c>
       <c r="AI16">
-        <v>0.011</v>
+        <v>0.025</v>
       </c>
       <c r="AJ16">
+        <v>0.014</v>
+      </c>
+      <c r="AK16">
+        <v>0.01</v>
+      </c>
+      <c r="AL16">
         <v>0.008</v>
       </c>
-      <c r="AK16">
-        <v>0.004</v>
-      </c>
-      <c r="AL16">
-        <v>0.003</v>
-      </c>
       <c r="AM16">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="AN16">
-        <v>0.594</v>
+        <v>0.56</v>
       </c>
       <c r="AO16">
-        <v>0.511</v>
+        <v>0.488</v>
       </c>
       <c r="AP16">
-        <v>0.568</v>
+        <v>0.526</v>
       </c>
       <c r="AQ16">
-        <v>0.536</v>
+        <v>0.542</v>
       </c>
       <c r="AR16">
-        <v>0.542</v>
+        <v>0.535</v>
       </c>
       <c r="AS16">
-        <v>0.499</v>
+        <v>0.522</v>
       </c>
       <c r="AT16">
-        <v>0.439</v>
+        <v>0.515</v>
       </c>
       <c r="AU16">
-        <v>0.455</v>
+        <v>0.54</v>
       </c>
       <c r="AV16">
-        <v>0.17</v>
+        <v>0.489</v>
       </c>
       <c r="AW16">
-        <v>0.125</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="17" spans="1:49">
       <c r="A17">
-        <v>823308</v>
+        <v>822746</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F17">
-        <v>5.028</v>
+        <v>4.251</v>
       </c>
       <c r="G17">
-        <v>0.61</v>
+        <v>0.493</v>
       </c>
       <c r="H17">
-        <v>0.117</v>
+        <v>0.099</v>
       </c>
       <c r="I17">
-        <v>0.327</v>
+        <v>0.223</v>
       </c>
       <c r="J17">
-        <v>0.09</v>
+        <v>0.091</v>
       </c>
       <c r="K17">
-        <v>0.196</v>
+        <v>0.286</v>
       </c>
       <c r="L17">
-        <v>1.268</v>
+        <v>0.746</v>
       </c>
       <c r="M17">
-        <v>0.108</v>
+        <v>0.114</v>
       </c>
       <c r="N17">
-        <v>1.543</v>
+        <v>1.672</v>
       </c>
       <c r="O17">
-        <v>5.634</v>
+        <v>5.602</v>
       </c>
       <c r="P17">
-        <v>3.85</v>
+        <v>3.568</v>
       </c>
       <c r="Q17">
-        <v>8.307</v>
+        <v>9.483</v>
       </c>
       <c r="R17">
-        <v>0.288</v>
+        <v>0.468</v>
       </c>
       <c r="S17">
-        <v>0.35</v>
+        <v>0.358</v>
       </c>
       <c r="T17">
-        <v>0.228</v>
+        <v>0.14</v>
       </c>
       <c r="U17">
-        <v>0.091</v>
+        <v>0.028</v>
       </c>
       <c r="V17">
-        <v>0.031</v>
+        <v>0.005</v>
       </c>
       <c r="W17">
-        <v>0.012</v>
+        <v>0.001</v>
       </c>
       <c r="X17">
-        <v>0.032</v>
+        <v>0.061</v>
       </c>
       <c r="Y17">
-        <v>0.077</v>
+        <v>0.101</v>
       </c>
       <c r="Z17">
-        <v>0.103</v>
+        <v>0.151</v>
       </c>
       <c r="AA17">
-        <v>0.14</v>
+        <v>0.136</v>
       </c>
       <c r="AB17">
-        <v>0.134</v>
+        <v>0.147</v>
       </c>
       <c r="AC17">
-        <v>0.131</v>
+        <v>0.121</v>
       </c>
       <c r="AD17">
-        <v>0.105</v>
+        <v>0.087</v>
       </c>
       <c r="AE17">
-        <v>0.082</v>
+        <v>0.064</v>
       </c>
       <c r="AF17">
-        <v>0.068</v>
+        <v>0.046</v>
       </c>
       <c r="AG17">
-        <v>0.042</v>
+        <v>0.033</v>
       </c>
       <c r="AH17">
-        <v>0.03</v>
+        <v>0.022</v>
       </c>
       <c r="AI17">
-        <v>0.022</v>
+        <v>0.013</v>
       </c>
       <c r="AJ17">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="AK17">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="AL17">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="AM17">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="AN17">
-        <v>0.59</v>
+        <v>0.447</v>
       </c>
       <c r="AO17">
-        <v>0.547</v>
+        <v>0.495</v>
       </c>
       <c r="AP17">
-        <v>0.552</v>
+        <v>0.488</v>
       </c>
       <c r="AQ17">
-        <v>0.58</v>
+        <v>0.468</v>
       </c>
       <c r="AR17">
-        <v>0.579</v>
+        <v>0.463</v>
       </c>
       <c r="AS17">
-        <v>0.556</v>
+        <v>0.443</v>
       </c>
       <c r="AT17">
-        <v>0.577</v>
+        <v>0.5</v>
       </c>
       <c r="AU17">
-        <v>0.579</v>
+        <v>0.471</v>
       </c>
       <c r="AV17">
-        <v>0.239</v>
+        <v>0.251</v>
       </c>
       <c r="AW17">
         <v>0.112</v>
@@ -3120,702 +3138,702 @@
     </row>
     <row r="18" spans="1:49">
       <c r="A18">
-        <v>823388</v>
+        <v>822988</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F18">
-        <v>4.762</v>
+        <v>3.957</v>
       </c>
       <c r="G18">
-        <v>0.614</v>
+        <v>0.438</v>
       </c>
       <c r="H18">
-        <v>0.113</v>
+        <v>0.089</v>
       </c>
       <c r="I18">
-        <v>0.316</v>
+        <v>0.186</v>
       </c>
       <c r="J18">
-        <v>0.089</v>
+        <v>0.104</v>
       </c>
       <c r="K18">
-        <v>0.194</v>
+        <v>0.33</v>
       </c>
       <c r="L18">
-        <v>0.903</v>
+        <v>0.729</v>
       </c>
       <c r="M18">
-        <v>0.124</v>
+        <v>0.085</v>
       </c>
       <c r="N18">
-        <v>1.877</v>
+        <v>1.342</v>
       </c>
       <c r="O18">
-        <v>5.445</v>
+        <v>5.13</v>
       </c>
       <c r="P18">
-        <v>4.104</v>
+        <v>4.096</v>
       </c>
       <c r="Q18">
-        <v>7.742</v>
+        <v>8.17</v>
       </c>
       <c r="R18">
-        <v>0.404</v>
+        <v>0.481</v>
       </c>
       <c r="S18">
-        <v>0.371</v>
+        <v>0.352</v>
       </c>
       <c r="T18">
-        <v>0.159</v>
+        <v>0.129</v>
       </c>
       <c r="U18">
-        <v>0.051</v>
+        <v>0.032</v>
       </c>
       <c r="V18">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="W18">
         <v>0.001</v>
       </c>
       <c r="X18">
-        <v>0.039</v>
+        <v>0.077</v>
       </c>
       <c r="Y18">
-        <v>0.077</v>
+        <v>0.13</v>
       </c>
       <c r="Z18">
-        <v>0.117</v>
+        <v>0.141</v>
       </c>
       <c r="AA18">
-        <v>0.141</v>
+        <v>0.143</v>
       </c>
       <c r="AB18">
-        <v>0.129</v>
+        <v>0.145</v>
       </c>
       <c r="AC18">
-        <v>0.137</v>
+        <v>0.108</v>
       </c>
       <c r="AD18">
-        <v>0.111</v>
+        <v>0.084</v>
       </c>
       <c r="AE18">
-        <v>0.084</v>
+        <v>0.061</v>
       </c>
       <c r="AF18">
-        <v>0.064</v>
+        <v>0.04</v>
       </c>
       <c r="AG18">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="AH18">
-        <v>0.022</v>
+        <v>0.015</v>
       </c>
       <c r="AI18">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="AJ18">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="AK18">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="AL18">
         <v>0.002</v>
       </c>
       <c r="AM18">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="AN18">
-        <v>0.62</v>
+        <v>0.416</v>
       </c>
       <c r="AO18">
-        <v>0.497</v>
+        <v>0.337</v>
       </c>
       <c r="AP18">
-        <v>0.576</v>
+        <v>0.4</v>
       </c>
       <c r="AQ18">
-        <v>0.494</v>
+        <v>0.396</v>
       </c>
       <c r="AR18">
-        <v>0.553</v>
+        <v>0.422</v>
       </c>
       <c r="AS18">
-        <v>0.508</v>
+        <v>0.412</v>
       </c>
       <c r="AT18">
-        <v>0.515</v>
+        <v>0.525</v>
       </c>
       <c r="AU18">
         <v>0.533</v>
       </c>
       <c r="AV18">
-        <v>0.227</v>
+        <v>0.301</v>
       </c>
       <c r="AW18">
-        <v>0.119</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="19" spans="1:49">
       <c r="A19">
-        <v>823715</v>
+        <v>823067</v>
       </c>
       <c r="B19" t="s">
         <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F19">
-        <v>4.592</v>
+        <v>4.051</v>
       </c>
       <c r="G19">
-        <v>0.541</v>
+        <v>0.43</v>
       </c>
       <c r="H19">
-        <v>0.104</v>
+        <v>0.093</v>
       </c>
       <c r="I19">
-        <v>0.27</v>
+        <v>0.187</v>
       </c>
       <c r="J19">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="K19">
-        <v>0.232</v>
+        <v>0.339</v>
       </c>
       <c r="L19">
-        <v>0.997</v>
+        <v>0.807</v>
       </c>
       <c r="M19">
-        <v>0.094</v>
+        <v>0.05</v>
       </c>
       <c r="N19">
-        <v>1.575</v>
+        <v>1.542</v>
       </c>
       <c r="O19">
-        <v>5.329</v>
+        <v>4.84</v>
       </c>
       <c r="P19">
-        <v>4.507</v>
+        <v>4.353</v>
       </c>
       <c r="Q19">
-        <v>10.741</v>
+        <v>7.892</v>
       </c>
       <c r="R19">
-        <v>0.377</v>
+        <v>0.457</v>
       </c>
       <c r="S19">
-        <v>0.353</v>
+        <v>0.342</v>
       </c>
       <c r="T19">
-        <v>0.189</v>
+        <v>0.151</v>
       </c>
       <c r="U19">
-        <v>0.062</v>
+        <v>0.042</v>
       </c>
       <c r="V19">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="W19">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="X19">
-        <v>0.052</v>
+        <v>0.069</v>
       </c>
       <c r="Y19">
-        <v>0.09</v>
+        <v>0.114</v>
       </c>
       <c r="Z19">
-        <v>0.124</v>
+        <v>0.142</v>
       </c>
       <c r="AA19">
-        <v>0.131</v>
+        <v>0.146</v>
       </c>
       <c r="AB19">
-        <v>0.141</v>
+        <v>0.137</v>
       </c>
       <c r="AC19">
-        <v>0.132</v>
+        <v>0.127</v>
       </c>
       <c r="AD19">
-        <v>0.096</v>
+        <v>0.091</v>
       </c>
       <c r="AE19">
-        <v>0.079</v>
+        <v>0.059</v>
       </c>
       <c r="AF19">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="AG19">
-        <v>0.041</v>
+        <v>0.028</v>
       </c>
       <c r="AH19">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="AI19">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="AJ19">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="AK19">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="AL19">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AM19">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AN19">
-        <v>0.597</v>
+        <v>0.531</v>
       </c>
       <c r="AO19">
-        <v>0.477</v>
+        <v>0.445</v>
       </c>
       <c r="AP19">
-        <v>0.54</v>
+        <v>0.478</v>
       </c>
       <c r="AQ19">
-        <v>0.493</v>
+        <v>0.451</v>
       </c>
       <c r="AR19">
-        <v>0.53</v>
+        <v>0.433</v>
       </c>
       <c r="AS19">
-        <v>0.525</v>
+        <v>0.42</v>
       </c>
       <c r="AT19">
-        <v>0.476</v>
+        <v>0.407</v>
       </c>
       <c r="AU19">
-        <v>0.487</v>
+        <v>0.4</v>
       </c>
       <c r="AV19">
-        <v>0.249</v>
+        <v>0.267</v>
       </c>
       <c r="AW19">
-        <v>0.115</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="20" spans="1:49">
       <c r="A20">
-        <v>823876</v>
+        <v>823144</v>
       </c>
       <c r="B20" t="s">
         <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F20">
-        <v>3.909</v>
+        <v>4.742</v>
       </c>
       <c r="G20">
-        <v>0.466</v>
+        <v>0.612</v>
       </c>
       <c r="H20">
-        <v>0.092</v>
+        <v>0.115</v>
       </c>
       <c r="I20">
-        <v>0.197</v>
+        <v>0.316</v>
       </c>
       <c r="J20">
-        <v>0.114</v>
+        <v>0.079</v>
       </c>
       <c r="K20">
-        <v>0.286</v>
+        <v>0.19</v>
       </c>
       <c r="L20">
-        <v>0.782</v>
+        <v>1.574</v>
       </c>
       <c r="M20">
-        <v>0.135</v>
+        <v>0.079</v>
       </c>
       <c r="N20">
-        <v>1.689</v>
+        <v>1.463</v>
       </c>
       <c r="O20">
-        <v>4.908</v>
+        <v>4.829</v>
       </c>
       <c r="P20">
-        <v>3.278</v>
+        <v>3.526</v>
       </c>
       <c r="Q20">
-        <v>8.276</v>
+        <v>8.403</v>
       </c>
       <c r="R20">
-        <v>0.458</v>
+        <v>0.203</v>
       </c>
       <c r="S20">
-        <v>0.357</v>
+        <v>0.322</v>
       </c>
       <c r="T20">
-        <v>0.136</v>
+        <v>0.272</v>
       </c>
       <c r="U20">
-        <v>0.042</v>
+        <v>0.134</v>
       </c>
       <c r="V20">
+        <v>0.049</v>
+      </c>
+      <c r="W20">
+        <v>0.021</v>
+      </c>
+      <c r="X20">
+        <v>0.032</v>
+      </c>
+      <c r="Y20">
+        <v>0.087</v>
+      </c>
+      <c r="Z20">
+        <v>0.112</v>
+      </c>
+      <c r="AA20">
+        <v>0.142</v>
+      </c>
+      <c r="AB20">
+        <v>0.144</v>
+      </c>
+      <c r="AC20">
+        <v>0.131</v>
+      </c>
+      <c r="AD20">
+        <v>0.104</v>
+      </c>
+      <c r="AE20">
+        <v>0.086</v>
+      </c>
+      <c r="AF20">
+        <v>0.053</v>
+      </c>
+      <c r="AG20">
+        <v>0.047</v>
+      </c>
+      <c r="AH20">
+        <v>0.024</v>
+      </c>
+      <c r="AI20">
+        <v>0.016</v>
+      </c>
+      <c r="AJ20">
+        <v>0.01</v>
+      </c>
+      <c r="AK20">
         <v>0.005</v>
       </c>
-      <c r="W20">
-        <v>0.001</v>
-      </c>
-      <c r="X20">
-        <v>0.07</v>
-      </c>
-      <c r="Y20">
-        <v>0.127</v>
-      </c>
-      <c r="Z20">
-        <v>0.147</v>
-      </c>
-      <c r="AA20">
-        <v>0.152</v>
-      </c>
-      <c r="AB20">
-        <v>0.135</v>
-      </c>
-      <c r="AC20">
-        <v>0.114</v>
-      </c>
-      <c r="AD20">
-        <v>0.094</v>
-      </c>
-      <c r="AE20">
-        <v>0.058</v>
-      </c>
-      <c r="AF20">
-        <v>0.045</v>
-      </c>
-      <c r="AG20">
-        <v>0.025</v>
-      </c>
-      <c r="AH20">
-        <v>0.016</v>
-      </c>
-      <c r="AI20">
-        <v>0.007</v>
-      </c>
-      <c r="AJ20">
-        <v>0.006</v>
-      </c>
-      <c r="AK20">
-        <v>0.002</v>
-      </c>
       <c r="AL20">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AM20">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AN20">
-        <v>0.449</v>
+        <v>0.644</v>
       </c>
       <c r="AO20">
-        <v>0.399</v>
+        <v>0.559</v>
       </c>
       <c r="AP20">
-        <v>0.475</v>
+        <v>0.591</v>
       </c>
       <c r="AQ20">
-        <v>0.416</v>
+        <v>0.558</v>
       </c>
       <c r="AR20">
-        <v>0.44</v>
+        <v>0.541</v>
       </c>
       <c r="AS20">
-        <v>0.426</v>
+        <v>0.514</v>
       </c>
       <c r="AT20">
-        <v>0.425</v>
+        <v>0.493</v>
       </c>
       <c r="AU20">
-        <v>0.423</v>
+        <v>0.447</v>
       </c>
       <c r="AV20">
-        <v>0.245</v>
+        <v>0.198</v>
       </c>
       <c r="AW20">
-        <v>0.114</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="21" spans="1:49">
       <c r="A21">
-        <v>824042</v>
+        <v>823308</v>
       </c>
       <c r="B21" t="s">
         <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F21">
-        <v>3.953</v>
+        <v>5.215</v>
       </c>
       <c r="G21">
-        <v>0.483</v>
+        <v>0.638</v>
       </c>
       <c r="H21">
-        <v>0.108</v>
+        <v>0.12</v>
       </c>
       <c r="I21">
-        <v>0.196</v>
+        <v>0.333</v>
       </c>
       <c r="J21">
-        <v>0.11</v>
+        <v>0.076</v>
       </c>
       <c r="K21">
-        <v>0.288</v>
+        <v>0.177</v>
       </c>
       <c r="L21">
-        <v>0.951</v>
+        <v>1.328</v>
       </c>
       <c r="M21">
-        <v>0.093</v>
+        <v>0.112</v>
       </c>
       <c r="N21">
-        <v>1.445</v>
+        <v>1.561</v>
       </c>
       <c r="O21">
-        <v>4.465</v>
+        <v>5.637</v>
       </c>
       <c r="P21">
-        <v>4.172</v>
+        <v>3.832</v>
       </c>
       <c r="Q21">
-        <v>11.629</v>
+        <v>8.146</v>
       </c>
       <c r="R21">
-        <v>0.395</v>
+        <v>0.262</v>
       </c>
       <c r="S21">
-        <v>0.358</v>
+        <v>0.347</v>
       </c>
       <c r="T21">
-        <v>0.172</v>
+        <v>0.245</v>
       </c>
       <c r="U21">
-        <v>0.055</v>
+        <v>0.102</v>
       </c>
       <c r="V21">
-        <v>0.015</v>
+        <v>0.034</v>
       </c>
       <c r="W21">
-        <v>0.005</v>
+        <v>0.009</v>
       </c>
       <c r="X21">
-        <v>0.074</v>
+        <v>0.028</v>
       </c>
       <c r="Y21">
-        <v>0.125</v>
+        <v>0.064</v>
       </c>
       <c r="Z21">
-        <v>0.148</v>
+        <v>0.092</v>
       </c>
       <c r="AA21">
-        <v>0.153</v>
+        <v>0.131</v>
       </c>
       <c r="AB21">
         <v>0.135</v>
       </c>
       <c r="AC21">
-        <v>0.117</v>
+        <v>0.133</v>
       </c>
       <c r="AD21">
-        <v>0.076</v>
+        <v>0.115</v>
       </c>
       <c r="AE21">
-        <v>0.063</v>
+        <v>0.099</v>
       </c>
       <c r="AF21">
-        <v>0.041</v>
+        <v>0.074</v>
       </c>
       <c r="AG21">
-        <v>0.028</v>
+        <v>0.04</v>
       </c>
       <c r="AH21">
-        <v>0.015</v>
+        <v>0.032</v>
       </c>
       <c r="AI21">
-        <v>0.01</v>
+        <v>0.026</v>
       </c>
       <c r="AJ21">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="AK21">
+        <v>0.008</v>
+      </c>
+      <c r="AL21">
         <v>0.004</v>
       </c>
-      <c r="AL21">
-        <v>0.001</v>
-      </c>
       <c r="AM21">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="AN21">
-        <v>0.418</v>
+        <v>0.625</v>
       </c>
       <c r="AO21">
-        <v>0.343</v>
+        <v>0.573</v>
       </c>
       <c r="AP21">
-        <v>0.356</v>
+        <v>0.591</v>
       </c>
       <c r="AQ21">
-        <v>0.362</v>
+        <v>0.572</v>
       </c>
       <c r="AR21">
-        <v>0.4</v>
+        <v>0.574</v>
       </c>
       <c r="AS21">
-        <v>0.484</v>
+        <v>0.555</v>
       </c>
       <c r="AT21">
-        <v>0.527</v>
+        <v>0.627</v>
       </c>
       <c r="AU21">
-        <v>0.555</v>
+        <v>0.595</v>
       </c>
       <c r="AV21">
-        <v>0.294</v>
+        <v>0.249</v>
       </c>
       <c r="AW21">
-        <v>0.117</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="22" spans="1:49">
       <c r="A22">
-        <v>824284</v>
+        <v>823388</v>
       </c>
       <c r="B22" t="s">
         <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F22">
-        <v>5.225</v>
+        <v>5.042</v>
       </c>
       <c r="G22">
-        <v>0.593</v>
+        <v>0.61</v>
       </c>
       <c r="H22">
-        <v>0.099</v>
+        <v>0.107</v>
       </c>
       <c r="I22">
-        <v>0.318</v>
+        <v>0.33</v>
       </c>
       <c r="J22">
-        <v>0.081</v>
+        <v>0.088</v>
       </c>
       <c r="K22">
-        <v>0.217</v>
+        <v>0.2</v>
       </c>
       <c r="L22">
-        <v>0.87</v>
+        <v>0.977</v>
       </c>
       <c r="M22">
-        <v>0.185</v>
+        <v>0.131</v>
       </c>
       <c r="N22">
-        <v>1.778</v>
+        <v>1.904</v>
       </c>
       <c r="O22">
-        <v>5.891</v>
+        <v>5.681</v>
       </c>
       <c r="P22">
-        <v>4.65</v>
+        <v>4.183</v>
       </c>
       <c r="Q22">
-        <v>6.516</v>
+        <v>7.692</v>
       </c>
       <c r="R22">
-        <v>0.417</v>
+        <v>0.379</v>
       </c>
       <c r="S22">
-        <v>0.371</v>
+        <v>0.362</v>
       </c>
       <c r="T22">
-        <v>0.152</v>
+        <v>0.181</v>
       </c>
       <c r="U22">
-        <v>0.047</v>
+        <v>0.061</v>
       </c>
       <c r="V22">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="W22">
         <v>0.002</v>
       </c>
       <c r="X22">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="Y22">
-        <v>0.069</v>
+        <v>0.071</v>
       </c>
       <c r="Z22">
-        <v>0.099</v>
+        <v>0.117</v>
       </c>
       <c r="AA22">
-        <v>0.127</v>
+        <v>0.135</v>
       </c>
       <c r="AB22">
-        <v>0.138</v>
+        <v>0.12</v>
       </c>
       <c r="AC22">
         <v>0.125</v>
       </c>
       <c r="AD22">
-        <v>0.108</v>
+        <v>0.116</v>
       </c>
       <c r="AE22">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="AF22">
-        <v>0.067</v>
+        <v>0.066</v>
       </c>
       <c r="AG22">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="AH22">
-        <v>0.035</v>
+        <v>0.031</v>
       </c>
       <c r="AI22">
         <v>0.023</v>
@@ -3824,490 +3842,1384 @@
         <v>0.013</v>
       </c>
       <c r="AK22">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AL22">
+        <v>0.004</v>
+      </c>
+      <c r="AM22">
         <v>0.008</v>
       </c>
-      <c r="AM22">
-        <v>0.009</v>
-      </c>
       <c r="AN22">
-        <v>0.622</v>
+        <v>0.659</v>
       </c>
       <c r="AO22">
-        <v>0.593</v>
+        <v>0.57</v>
       </c>
       <c r="AP22">
-        <v>0.616</v>
+        <v>0.59</v>
       </c>
       <c r="AQ22">
-        <v>0.594</v>
+        <v>0.574</v>
       </c>
       <c r="AR22">
-        <v>0.614</v>
+        <v>0.528</v>
       </c>
       <c r="AS22">
-        <v>0.596</v>
+        <v>0.555</v>
       </c>
       <c r="AT22">
+        <v>0.556</v>
+      </c>
+      <c r="AU22">
         <v>0.529</v>
       </c>
-      <c r="AU22">
-        <v>0.547</v>
-      </c>
       <c r="AV22">
-        <v>0.261</v>
+        <v>0.23</v>
       </c>
       <c r="AW22">
-        <v>0.113</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="23" spans="1:49">
       <c r="A23">
-        <v>824685</v>
+        <v>823554</v>
       </c>
       <c r="B23" t="s">
         <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E23" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F23">
-        <v>4.682</v>
+        <v>4.829</v>
       </c>
       <c r="G23">
-        <v>0.591</v>
+        <v>0.573</v>
       </c>
       <c r="H23">
+        <v>0.11</v>
+      </c>
+      <c r="I23">
+        <v>0.285</v>
+      </c>
+      <c r="J23">
+        <v>0.081</v>
+      </c>
+      <c r="K23">
+        <v>0.242</v>
+      </c>
+      <c r="L23">
+        <v>1.142</v>
+      </c>
+      <c r="M23">
+        <v>0.099</v>
+      </c>
+      <c r="N23">
+        <v>1.322</v>
+      </c>
+      <c r="O23">
+        <v>5.118</v>
+      </c>
+      <c r="P23">
+        <v>5.171</v>
+      </c>
+      <c r="Q23">
+        <v>10.007</v>
+      </c>
+      <c r="R23">
+        <v>0.319</v>
+      </c>
+      <c r="S23">
+        <v>0.364</v>
+      </c>
+      <c r="T23">
+        <v>0.21</v>
+      </c>
+      <c r="U23">
+        <v>0.078</v>
+      </c>
+      <c r="V23">
+        <v>0.021</v>
+      </c>
+      <c r="W23">
+        <v>0.008</v>
+      </c>
+      <c r="X23">
+        <v>0.048</v>
+      </c>
+      <c r="Y23">
+        <v>0.077</v>
+      </c>
+      <c r="Z23">
         <v>0.107</v>
       </c>
-      <c r="I23">
-        <v>0.305</v>
-      </c>
-      <c r="J23">
+      <c r="AA23">
+        <v>0.134</v>
+      </c>
+      <c r="AB23">
+        <v>0.131</v>
+      </c>
+      <c r="AC23">
+        <v>0.13</v>
+      </c>
+      <c r="AD23">
+        <v>0.113</v>
+      </c>
+      <c r="AE23">
         <v>0.087</v>
       </c>
-      <c r="K23">
-        <v>0.203</v>
-      </c>
-      <c r="L23">
-        <v>0.783</v>
-      </c>
-      <c r="M23">
-        <v>0.133</v>
-      </c>
-      <c r="N23">
-        <v>1.598</v>
-      </c>
-      <c r="O23">
-        <v>6.001</v>
-      </c>
-      <c r="P23">
-        <v>4.077</v>
-      </c>
-      <c r="Q23">
-        <v>7.068</v>
-      </c>
-      <c r="R23">
-        <v>0.457</v>
-      </c>
-      <c r="S23">
-        <v>0.36</v>
-      </c>
-      <c r="T23">
-        <v>0.139</v>
-      </c>
-      <c r="U23">
-        <v>0.035</v>
-      </c>
-      <c r="V23">
-        <v>0.009</v>
-      </c>
-      <c r="W23">
-        <v>0.001</v>
-      </c>
-      <c r="X23">
-        <v>0.044</v>
-      </c>
-      <c r="Y23">
-        <v>0.08</v>
-      </c>
-      <c r="Z23">
-        <v>0.111</v>
-      </c>
-      <c r="AA23">
-        <v>0.143</v>
-      </c>
-      <c r="AB23">
-        <v>0.146</v>
-      </c>
-      <c r="AC23">
-        <v>0.136</v>
-      </c>
-      <c r="AD23">
-        <v>0.102</v>
-      </c>
-      <c r="AE23">
-        <v>0.08</v>
-      </c>
       <c r="AF23">
-        <v>0.054</v>
+        <v>0.06</v>
       </c>
       <c r="AG23">
         <v>0.046</v>
       </c>
       <c r="AH23">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
       <c r="AI23">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AJ23">
         <v>0.009</v>
       </c>
       <c r="AK23">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="AL23">
         <v>0.004</v>
       </c>
       <c r="AM23">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="AN23">
-        <v>0.554</v>
+        <v>0.61</v>
       </c>
       <c r="AO23">
-        <v>0.542</v>
+        <v>0.534</v>
       </c>
       <c r="AP23">
-        <v>0.519</v>
+        <v>0.608</v>
       </c>
       <c r="AQ23">
-        <v>0.542</v>
+        <v>0.543</v>
       </c>
       <c r="AR23">
-        <v>0.547</v>
+        <v>0.545</v>
       </c>
       <c r="AS23">
-        <v>0.505</v>
+        <v>0.509</v>
       </c>
       <c r="AT23">
-        <v>0.491</v>
+        <v>0.504</v>
       </c>
       <c r="AU23">
-        <v>0.521</v>
+        <v>0.507</v>
       </c>
       <c r="AV23">
-        <v>0.208</v>
+        <v>0.255</v>
       </c>
       <c r="AW23">
-        <v>0.118</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="24" spans="1:49">
       <c r="A24">
-        <v>824771</v>
+        <v>823715</v>
       </c>
       <c r="B24" t="s">
         <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E24" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F24">
-        <v>5.454</v>
+        <v>4.698</v>
       </c>
       <c r="G24">
-        <v>0.575</v>
+        <v>0.57</v>
       </c>
       <c r="H24">
-        <v>0.112</v>
+        <v>0.104</v>
       </c>
       <c r="I24">
-        <v>0.3</v>
+        <v>0.285</v>
       </c>
       <c r="J24">
-        <v>0.08</v>
+        <v>0.083</v>
       </c>
       <c r="K24">
-        <v>0.233</v>
+        <v>0.22</v>
       </c>
       <c r="L24">
-        <v>1.149</v>
+        <v>0.949</v>
       </c>
       <c r="M24">
-        <v>0.186</v>
+        <v>0.088</v>
       </c>
       <c r="N24">
-        <v>2.162</v>
+        <v>1.557</v>
       </c>
       <c r="O24">
-        <v>5.5</v>
+        <v>5.618</v>
       </c>
       <c r="P24">
-        <v>4.366</v>
+        <v>4.566</v>
       </c>
       <c r="Q24">
-        <v>8.313</v>
+        <v>10.183</v>
       </c>
       <c r="R24">
-        <v>0.311</v>
+        <v>0.374</v>
       </c>
       <c r="S24">
-        <v>0.373</v>
+        <v>0.384</v>
       </c>
       <c r="T24">
-        <v>0.211</v>
+        <v>0.177</v>
       </c>
       <c r="U24">
-        <v>0.076</v>
+        <v>0.051</v>
       </c>
       <c r="V24">
-        <v>0.022</v>
+        <v>0.012</v>
       </c>
       <c r="W24">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="X24">
-        <v>0.025</v>
+        <v>0.051</v>
       </c>
       <c r="Y24">
-        <v>0.05</v>
+        <v>0.085</v>
       </c>
       <c r="Z24">
-        <v>0.095</v>
+        <v>0.119</v>
       </c>
       <c r="AA24">
-        <v>0.124</v>
+        <v>0.122</v>
       </c>
       <c r="AB24">
-        <v>0.135</v>
+        <v>0.137</v>
       </c>
       <c r="AC24">
-        <v>0.136</v>
+        <v>0.14</v>
       </c>
       <c r="AD24">
-        <v>0.108</v>
+        <v>0.094</v>
       </c>
       <c r="AE24">
-        <v>0.087</v>
+        <v>0.081</v>
       </c>
       <c r="AF24">
-        <v>0.078</v>
+        <v>0.064</v>
       </c>
       <c r="AG24">
-        <v>0.054</v>
+        <v>0.039</v>
       </c>
       <c r="AH24">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
       <c r="AI24">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="AJ24">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="AK24">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="AL24">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="AM24">
-        <v>0.009</v>
+        <v>0.004</v>
       </c>
       <c r="AN24">
-        <v>0.73</v>
+        <v>0.546</v>
       </c>
       <c r="AO24">
-        <v>0.598</v>
+        <v>0.538</v>
       </c>
       <c r="AP24">
-        <v>0.663</v>
+        <v>0.571</v>
       </c>
       <c r="AQ24">
-        <v>0.661</v>
+        <v>0.543</v>
       </c>
       <c r="AR24">
-        <v>0.614</v>
+        <v>0.526</v>
       </c>
       <c r="AS24">
-        <v>0.597</v>
+        <v>0.539</v>
       </c>
       <c r="AT24">
-        <v>0.537</v>
+        <v>0.505</v>
       </c>
       <c r="AU24">
-        <v>0.545</v>
+        <v>0.452</v>
       </c>
       <c r="AV24">
-        <v>0.249</v>
+        <v>0.237</v>
       </c>
       <c r="AW24">
-        <v>0.122</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="25" spans="1:49">
       <c r="A25">
-        <v>825014</v>
+        <v>823876</v>
       </c>
       <c r="B25" t="s">
         <v>49</v>
       </c>
       <c r="C25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25">
+        <v>4.031</v>
+      </c>
+      <c r="G25">
+        <v>0.48</v>
+      </c>
+      <c r="H25">
+        <v>0.085</v>
+      </c>
+      <c r="I25">
+        <v>0.213</v>
+      </c>
+      <c r="J25">
+        <v>0.099</v>
+      </c>
+      <c r="K25">
+        <v>0.288</v>
+      </c>
+      <c r="L25">
+        <v>0.756</v>
+      </c>
+      <c r="M25">
+        <v>0.116</v>
+      </c>
+      <c r="N25">
+        <v>1.453</v>
+      </c>
+      <c r="O25">
+        <v>5.404</v>
+      </c>
+      <c r="P25">
+        <v>3.606</v>
+      </c>
+      <c r="Q25">
+        <v>7.582</v>
+      </c>
+      <c r="R25">
+        <v>0.467</v>
+      </c>
+      <c r="S25">
+        <v>0.36</v>
+      </c>
+      <c r="T25">
+        <v>0.132</v>
+      </c>
+      <c r="U25">
+        <v>0.034</v>
+      </c>
+      <c r="V25">
+        <v>0.007</v>
+      </c>
+      <c r="W25">
+        <v>0.001</v>
+      </c>
+      <c r="X25">
+        <v>0.068</v>
+      </c>
+      <c r="Y25">
+        <v>0.121</v>
+      </c>
+      <c r="Z25">
+        <v>0.127</v>
+      </c>
+      <c r="AA25">
+        <v>0.159</v>
+      </c>
+      <c r="AB25">
+        <v>0.145</v>
+      </c>
+      <c r="AC25">
+        <v>0.119</v>
+      </c>
+      <c r="AD25">
+        <v>0.092</v>
+      </c>
+      <c r="AE25">
+        <v>0.063</v>
+      </c>
+      <c r="AF25">
+        <v>0.036</v>
+      </c>
+      <c r="AG25">
+        <v>0.03</v>
+      </c>
+      <c r="AH25">
+        <v>0.019</v>
+      </c>
+      <c r="AI25">
+        <v>0.01</v>
+      </c>
+      <c r="AJ25">
+        <v>0.005</v>
+      </c>
+      <c r="AK25">
+        <v>0.002</v>
+      </c>
+      <c r="AL25">
+        <v>0.001</v>
+      </c>
+      <c r="AM25">
+        <v>0.003</v>
+      </c>
+      <c r="AN25">
+        <v>0.513</v>
+      </c>
+      <c r="AO25">
+        <v>0.439</v>
+      </c>
+      <c r="AP25">
+        <v>0.46</v>
+      </c>
+      <c r="AQ25">
+        <v>0.425</v>
+      </c>
+      <c r="AR25">
+        <v>0.444</v>
+      </c>
+      <c r="AS25">
+        <v>0.434</v>
+      </c>
+      <c r="AT25">
+        <v>0.447</v>
+      </c>
+      <c r="AU25">
+        <v>0.433</v>
+      </c>
+      <c r="AV25">
+        <v>0.223</v>
+      </c>
+      <c r="AW25">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49">
+      <c r="A26">
+        <v>824042</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26">
+        <v>4.047</v>
+      </c>
+      <c r="G26">
+        <v>0.481</v>
+      </c>
+      <c r="H26">
+        <v>0.1</v>
+      </c>
+      <c r="I26">
+        <v>0.209</v>
+      </c>
+      <c r="J26">
+        <v>0.089</v>
+      </c>
+      <c r="K26">
+        <v>0.3</v>
+      </c>
+      <c r="L26">
+        <v>1.009</v>
+      </c>
+      <c r="M26">
+        <v>0.102</v>
+      </c>
+      <c r="N26">
+        <v>1.467</v>
+      </c>
+      <c r="O26">
+        <v>4.451</v>
+      </c>
+      <c r="P26">
+        <v>4.162</v>
+      </c>
+      <c r="Q26">
+        <v>11.549</v>
+      </c>
+      <c r="R26">
+        <v>0.364</v>
+      </c>
+      <c r="S26">
+        <v>0.368</v>
+      </c>
+      <c r="T26">
+        <v>0.189</v>
+      </c>
+      <c r="U26">
+        <v>0.06</v>
+      </c>
+      <c r="V26">
+        <v>0.015</v>
+      </c>
+      <c r="W26">
+        <v>0.004</v>
+      </c>
+      <c r="X26">
+        <v>0.074</v>
+      </c>
+      <c r="Y26">
+        <v>0.112</v>
+      </c>
+      <c r="Z26">
+        <v>0.139</v>
+      </c>
+      <c r="AA26">
+        <v>0.16</v>
+      </c>
+      <c r="AB26">
+        <v>0.127</v>
+      </c>
+      <c r="AC26">
+        <v>0.121</v>
+      </c>
+      <c r="AD26">
+        <v>0.086</v>
+      </c>
+      <c r="AE26">
+        <v>0.064</v>
+      </c>
+      <c r="AF26">
+        <v>0.048</v>
+      </c>
+      <c r="AG26">
+        <v>0.024</v>
+      </c>
+      <c r="AH26">
+        <v>0.018</v>
+      </c>
+      <c r="AI26">
+        <v>0.012</v>
+      </c>
+      <c r="AJ26">
+        <v>0.006</v>
+      </c>
+      <c r="AK26">
+        <v>0.004</v>
+      </c>
+      <c r="AL26">
+        <v>0.002</v>
+      </c>
+      <c r="AM26">
+        <v>0.002</v>
+      </c>
+      <c r="AN26">
+        <v>0.43</v>
+      </c>
+      <c r="AO26">
+        <v>0.365</v>
+      </c>
+      <c r="AP26">
+        <v>0.382</v>
+      </c>
+      <c r="AQ26">
+        <v>0.384</v>
+      </c>
+      <c r="AR26">
+        <v>0.397</v>
+      </c>
+      <c r="AS26">
+        <v>0.481</v>
+      </c>
+      <c r="AT26">
+        <v>0.523</v>
+      </c>
+      <c r="AU26">
+        <v>0.557</v>
+      </c>
+      <c r="AV26">
+        <v>0.322</v>
+      </c>
+      <c r="AW26">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:49">
+      <c r="A27">
+        <v>824284</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27">
+        <v>5.398</v>
+      </c>
+      <c r="G27">
+        <v>0.606</v>
+      </c>
+      <c r="H27">
+        <v>0.102</v>
+      </c>
+      <c r="I27">
+        <v>0.326</v>
+      </c>
+      <c r="J27">
+        <v>0.08</v>
+      </c>
+      <c r="K27">
+        <v>0.203</v>
+      </c>
+      <c r="L27">
+        <v>0.961</v>
+      </c>
+      <c r="M27">
+        <v>0.169</v>
+      </c>
+      <c r="N27">
+        <v>1.809</v>
+      </c>
+      <c r="O27">
+        <v>5.952</v>
+      </c>
+      <c r="P27">
+        <v>4.582</v>
+      </c>
+      <c r="Q27">
+        <v>6.479</v>
+      </c>
+      <c r="R27">
+        <v>0.395</v>
+      </c>
+      <c r="S27">
+        <v>0.351</v>
+      </c>
+      <c r="T27">
+        <v>0.175</v>
+      </c>
+      <c r="U27">
+        <v>0.059</v>
+      </c>
+      <c r="V27">
+        <v>0.015</v>
+      </c>
+      <c r="W27">
+        <v>0.004</v>
+      </c>
+      <c r="X27">
+        <v>0.028</v>
+      </c>
+      <c r="Y27">
+        <v>0.059</v>
+      </c>
+      <c r="Z27">
+        <v>0.111</v>
+      </c>
+      <c r="AA27">
+        <v>0.117</v>
+      </c>
+      <c r="AB27">
+        <v>0.126</v>
+      </c>
+      <c r="AC27">
+        <v>0.128</v>
+      </c>
+      <c r="AD27">
+        <v>0.101</v>
+      </c>
+      <c r="AE27">
+        <v>0.098</v>
+      </c>
+      <c r="AF27">
+        <v>0.068</v>
+      </c>
+      <c r="AG27">
+        <v>0.052</v>
+      </c>
+      <c r="AH27">
+        <v>0.039</v>
+      </c>
+      <c r="AI27">
+        <v>0.024</v>
+      </c>
+      <c r="AJ27">
+        <v>0.017</v>
+      </c>
+      <c r="AK27">
+        <v>0.011</v>
+      </c>
+      <c r="AL27">
+        <v>0.008</v>
+      </c>
+      <c r="AM27">
+        <v>0.012</v>
+      </c>
+      <c r="AN27">
+        <v>0.658</v>
+      </c>
+      <c r="AO27">
+        <v>0.647</v>
+      </c>
+      <c r="AP27">
+        <v>0.63</v>
+      </c>
+      <c r="AQ27">
+        <v>0.637</v>
+      </c>
+      <c r="AR27">
+        <v>0.612</v>
+      </c>
+      <c r="AS27">
+        <v>0.624</v>
+      </c>
+      <c r="AT27">
+        <v>0.555</v>
+      </c>
+      <c r="AU27">
+        <v>0.544</v>
+      </c>
+      <c r="AV27">
+        <v>0.245</v>
+      </c>
+      <c r="AW27">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:49">
+      <c r="A28">
+        <v>824365</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28">
+        <v>4.789</v>
+      </c>
+      <c r="G28">
+        <v>0.405</v>
+      </c>
+      <c r="H28">
+        <v>0.085</v>
+      </c>
+      <c r="I28">
+        <v>0.177</v>
+      </c>
+      <c r="J28">
+        <v>0.1</v>
+      </c>
+      <c r="K28">
+        <v>0.389</v>
+      </c>
+      <c r="L28">
+        <v>1.239</v>
+      </c>
+      <c r="M28">
+        <v>0.154</v>
+      </c>
+      <c r="N28">
+        <v>1.686</v>
+      </c>
+      <c r="O28">
+        <v>5.691</v>
+      </c>
+      <c r="P28">
+        <v>2.74</v>
+      </c>
+      <c r="Q28">
+        <v>8.507</v>
+      </c>
+      <c r="R28">
+        <v>0.294</v>
+      </c>
+      <c r="S28">
+        <v>0.354</v>
+      </c>
+      <c r="T28">
+        <v>0.22</v>
+      </c>
+      <c r="U28">
+        <v>0.094</v>
+      </c>
+      <c r="V28">
+        <v>0.028</v>
+      </c>
+      <c r="W28">
+        <v>0.01</v>
+      </c>
+      <c r="X28">
+        <v>0.044</v>
+      </c>
+      <c r="Y28">
+        <v>0.091</v>
+      </c>
+      <c r="Z28">
+        <v>0.126</v>
+      </c>
+      <c r="AA28">
+        <v>0.131</v>
+      </c>
+      <c r="AB28">
+        <v>0.129</v>
+      </c>
+      <c r="AC28">
+        <v>0.12</v>
+      </c>
+      <c r="AD28">
+        <v>0.101</v>
+      </c>
+      <c r="AE28">
+        <v>0.076</v>
+      </c>
+      <c r="AF28">
+        <v>0.057</v>
+      </c>
+      <c r="AG28">
+        <v>0.041</v>
+      </c>
+      <c r="AH28">
+        <v>0.034</v>
+      </c>
+      <c r="AI28">
+        <v>0.022</v>
+      </c>
+      <c r="AJ28">
+        <v>0.011</v>
+      </c>
+      <c r="AK28">
+        <v>0.007</v>
+      </c>
+      <c r="AL28">
+        <v>0.004</v>
+      </c>
+      <c r="AM28">
+        <v>0.007</v>
+      </c>
+      <c r="AN28">
+        <v>0.465</v>
+      </c>
+      <c r="AO28">
+        <v>0.462</v>
+      </c>
+      <c r="AP28">
+        <v>0.46</v>
+      </c>
+      <c r="AQ28">
+        <v>0.492</v>
+      </c>
+      <c r="AR28">
+        <v>0.506</v>
+      </c>
+      <c r="AS28">
+        <v>0.549</v>
+      </c>
+      <c r="AT28">
+        <v>0.598</v>
+      </c>
+      <c r="AU28">
+        <v>0.629</v>
+      </c>
+      <c r="AV28">
+        <v>0.396</v>
+      </c>
+      <c r="AW28">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:49">
+      <c r="A29">
+        <v>824685</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" t="s">
         <v>75</v>
       </c>
-      <c r="D25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25">
-        <v>6.302</v>
-      </c>
-      <c r="G25">
-        <v>0.627</v>
-      </c>
-      <c r="H25">
+      <c r="F29">
+        <v>4.586</v>
+      </c>
+      <c r="G29">
+        <v>0.587</v>
+      </c>
+      <c r="H29">
+        <v>0.116</v>
+      </c>
+      <c r="I29">
+        <v>0.289</v>
+      </c>
+      <c r="J29">
+        <v>0.09</v>
+      </c>
+      <c r="K29">
+        <v>0.204</v>
+      </c>
+      <c r="L29">
+        <v>0.818</v>
+      </c>
+      <c r="M29">
+        <v>0.13</v>
+      </c>
+      <c r="N29">
+        <v>1.52</v>
+      </c>
+      <c r="O29">
+        <v>5.912</v>
+      </c>
+      <c r="P29">
+        <v>4.029</v>
+      </c>
+      <c r="Q29">
+        <v>7.042</v>
+      </c>
+      <c r="R29">
+        <v>0.441</v>
+      </c>
+      <c r="S29">
+        <v>0.359</v>
+      </c>
+      <c r="T29">
+        <v>0.151</v>
+      </c>
+      <c r="U29">
+        <v>0.04</v>
+      </c>
+      <c r="V29">
+        <v>0.008</v>
+      </c>
+      <c r="W29">
+        <v>0.001</v>
+      </c>
+      <c r="X29">
+        <v>0.043</v>
+      </c>
+      <c r="Y29">
+        <v>0.086</v>
+      </c>
+      <c r="Z29">
+        <v>0.124</v>
+      </c>
+      <c r="AA29">
+        <v>0.143</v>
+      </c>
+      <c r="AB29">
+        <v>0.147</v>
+      </c>
+      <c r="AC29">
+        <v>0.128</v>
+      </c>
+      <c r="AD29">
         <v>0.097</v>
       </c>
-      <c r="I25">
-        <v>0.376</v>
-      </c>
-      <c r="J25">
-        <v>0.074</v>
-      </c>
-      <c r="K25">
-        <v>0.209</v>
-      </c>
-      <c r="L25">
-        <v>1.8</v>
-      </c>
-      <c r="M25">
-        <v>0.14</v>
-      </c>
-      <c r="N25">
-        <v>2.022</v>
-      </c>
-      <c r="O25">
-        <v>5.955</v>
-      </c>
-      <c r="P25">
-        <v>3.812</v>
-      </c>
-      <c r="Q25">
-        <v>7.27</v>
-      </c>
-      <c r="R25">
-        <v>0.159</v>
-      </c>
-      <c r="S25">
-        <v>0.304</v>
-      </c>
-      <c r="T25">
-        <v>0.268</v>
-      </c>
-      <c r="U25">
-        <v>0.165</v>
-      </c>
-      <c r="V25">
-        <v>0.067</v>
-      </c>
-      <c r="W25">
+      <c r="AE29">
+        <v>0.076</v>
+      </c>
+      <c r="AF29">
+        <v>0.058</v>
+      </c>
+      <c r="AG29">
         <v>0.036</v>
       </c>
-      <c r="X25">
+      <c r="AH29">
+        <v>0.029</v>
+      </c>
+      <c r="AI29">
+        <v>0.011</v>
+      </c>
+      <c r="AJ29">
+        <v>0.01</v>
+      </c>
+      <c r="AK29">
+        <v>0.005</v>
+      </c>
+      <c r="AL29">
+        <v>0.004</v>
+      </c>
+      <c r="AM29">
+        <v>0.002</v>
+      </c>
+      <c r="AN29">
+        <v>0.569</v>
+      </c>
+      <c r="AO29">
+        <v>0.503</v>
+      </c>
+      <c r="AP29">
+        <v>0.537</v>
+      </c>
+      <c r="AQ29">
+        <v>0.508</v>
+      </c>
+      <c r="AR29">
+        <v>0.506</v>
+      </c>
+      <c r="AS29">
+        <v>0.482</v>
+      </c>
+      <c r="AT29">
+        <v>0.484</v>
+      </c>
+      <c r="AU29">
+        <v>0.503</v>
+      </c>
+      <c r="AV29">
+        <v>0.234</v>
+      </c>
+      <c r="AW29">
+        <v>0.139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:49">
+      <c r="A30">
+        <v>824771</v>
+      </c>
+      <c r="B30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30">
+        <v>5.591</v>
+      </c>
+      <c r="G30">
+        <v>0.596</v>
+      </c>
+      <c r="H30">
+        <v>0.1</v>
+      </c>
+      <c r="I30">
+        <v>0.318</v>
+      </c>
+      <c r="J30">
+        <v>0.077</v>
+      </c>
+      <c r="K30">
+        <v>0.238</v>
+      </c>
+      <c r="L30">
+        <v>1.128</v>
+      </c>
+      <c r="M30">
+        <v>0.19</v>
+      </c>
+      <c r="N30">
+        <v>2.249</v>
+      </c>
+      <c r="O30">
+        <v>5.495</v>
+      </c>
+      <c r="P30">
+        <v>4.423</v>
+      </c>
+      <c r="Q30">
+        <v>8.18</v>
+      </c>
+      <c r="R30">
+        <v>0.321</v>
+      </c>
+      <c r="S30">
+        <v>0.381</v>
+      </c>
+      <c r="T30">
+        <v>0.186</v>
+      </c>
+      <c r="U30">
+        <v>0.079</v>
+      </c>
+      <c r="V30">
+        <v>0.024</v>
+      </c>
+      <c r="W30">
+        <v>0.008</v>
+      </c>
+      <c r="X30">
+        <v>0.025</v>
+      </c>
+      <c r="Y30">
+        <v>0.057</v>
+      </c>
+      <c r="Z30">
+        <v>0.087</v>
+      </c>
+      <c r="AA30">
+        <v>0.119</v>
+      </c>
+      <c r="AB30">
+        <v>0.125</v>
+      </c>
+      <c r="AC30">
+        <v>0.127</v>
+      </c>
+      <c r="AD30">
+        <v>0.12</v>
+      </c>
+      <c r="AE30">
+        <v>0.099</v>
+      </c>
+      <c r="AF30">
+        <v>0.069</v>
+      </c>
+      <c r="AG30">
+        <v>0.05</v>
+      </c>
+      <c r="AH30">
+        <v>0.037</v>
+      </c>
+      <c r="AI30">
+        <v>0.03</v>
+      </c>
+      <c r="AJ30">
+        <v>0.016</v>
+      </c>
+      <c r="AK30">
+        <v>0.015</v>
+      </c>
+      <c r="AL30">
+        <v>0.008</v>
+      </c>
+      <c r="AM30">
+        <v>0.016</v>
+      </c>
+      <c r="AN30">
+        <v>0.714</v>
+      </c>
+      <c r="AO30">
+        <v>0.646</v>
+      </c>
+      <c r="AP30">
+        <v>0.7</v>
+      </c>
+      <c r="AQ30">
+        <v>0.659</v>
+      </c>
+      <c r="AR30">
+        <v>0.629</v>
+      </c>
+      <c r="AS30">
+        <v>0.621</v>
+      </c>
+      <c r="AT30">
+        <v>0.557</v>
+      </c>
+      <c r="AU30">
+        <v>0.577</v>
+      </c>
+      <c r="AV30">
+        <v>0.255</v>
+      </c>
+      <c r="AW30">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="31" spans="1:49">
+      <c r="A31">
+        <v>825014</v>
+      </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31">
+        <v>6.02</v>
+      </c>
+      <c r="G31">
+        <v>0.624</v>
+      </c>
+      <c r="H31">
+        <v>0.112</v>
+      </c>
+      <c r="I31">
+        <v>0.356</v>
+      </c>
+      <c r="J31">
+        <v>0.082</v>
+      </c>
+      <c r="K31">
+        <v>0.193</v>
+      </c>
+      <c r="L31">
+        <v>1.723</v>
+      </c>
+      <c r="M31">
+        <v>0.134</v>
+      </c>
+      <c r="N31">
+        <v>2.14</v>
+      </c>
+      <c r="O31">
+        <v>5.495</v>
+      </c>
+      <c r="P31">
+        <v>3.86</v>
+      </c>
+      <c r="Q31">
+        <v>7.262</v>
+      </c>
+      <c r="R31">
+        <v>0.172</v>
+      </c>
+      <c r="S31">
+        <v>0.314</v>
+      </c>
+      <c r="T31">
+        <v>0.267</v>
+      </c>
+      <c r="U31">
+        <v>0.151</v>
+      </c>
+      <c r="V31">
+        <v>0.069</v>
+      </c>
+      <c r="W31">
+        <v>0.027</v>
+      </c>
+      <c r="X31">
+        <v>0.022</v>
+      </c>
+      <c r="Y31">
+        <v>0.037</v>
+      </c>
+      <c r="Z31">
+        <v>0.076</v>
+      </c>
+      <c r="AA31">
+        <v>0.096</v>
+      </c>
+      <c r="AB31">
+        <v>0.118</v>
+      </c>
+      <c r="AC31">
+        <v>0.124</v>
+      </c>
+      <c r="AD31">
+        <v>0.13</v>
+      </c>
+      <c r="AE31">
+        <v>0.103</v>
+      </c>
+      <c r="AF31">
+        <v>0.087</v>
+      </c>
+      <c r="AG31">
+        <v>0.068</v>
+      </c>
+      <c r="AH31">
+        <v>0.045</v>
+      </c>
+      <c r="AI31">
+        <v>0.034</v>
+      </c>
+      <c r="AJ31">
+        <v>0.023</v>
+      </c>
+      <c r="AK31">
+        <v>0.016</v>
+      </c>
+      <c r="AL31">
+        <v>0.008</v>
+      </c>
+      <c r="AM31">
         <v>0.014</v>
       </c>
-      <c r="Y25">
-        <v>0.046</v>
-      </c>
-      <c r="Z25">
-        <v>0.063</v>
-      </c>
-      <c r="AA25">
+      <c r="AN31">
+        <v>0.866</v>
+      </c>
+      <c r="AO31">
+        <v>0.7</v>
+      </c>
+      <c r="AP31">
+        <v>0.768</v>
+      </c>
+      <c r="AQ31">
+        <v>0.699</v>
+      </c>
+      <c r="AR31">
+        <v>0.695</v>
+      </c>
+      <c r="AS31">
+        <v>0.628</v>
+      </c>
+      <c r="AT31">
+        <v>0.641</v>
+      </c>
+      <c r="AU31">
+        <v>0.573</v>
+      </c>
+      <c r="AV31">
+        <v>0.222</v>
+      </c>
+      <c r="AW31">
         <v>0.102</v>
-      </c>
-      <c r="AB25">
-        <v>0.103</v>
-      </c>
-      <c r="AC25">
-        <v>0.12</v>
-      </c>
-      <c r="AD25">
-        <v>0.12</v>
-      </c>
-      <c r="AE25">
-        <v>0.103</v>
-      </c>
-      <c r="AF25">
-        <v>0.092</v>
-      </c>
-      <c r="AG25">
-        <v>0.072</v>
-      </c>
-      <c r="AH25">
-        <v>0.052</v>
-      </c>
-      <c r="AI25">
-        <v>0.035</v>
-      </c>
-      <c r="AJ25">
-        <v>0.023</v>
-      </c>
-      <c r="AK25">
-        <v>0.019</v>
-      </c>
-      <c r="AL25">
-        <v>0.014</v>
-      </c>
-      <c r="AM25">
-        <v>0.022</v>
-      </c>
-      <c r="AN25">
-        <v>0.862</v>
-      </c>
-      <c r="AO25">
-        <v>0.783</v>
-      </c>
-      <c r="AP25">
-        <v>0.765</v>
-      </c>
-      <c r="AQ25">
-        <v>0.74</v>
-      </c>
-      <c r="AR25">
-        <v>0.764</v>
-      </c>
-      <c r="AS25">
-        <v>0.668</v>
-      </c>
-      <c r="AT25">
-        <v>0.663</v>
-      </c>
-      <c r="AU25">
-        <v>0.584</v>
-      </c>
-      <c r="AV25">
-        <v>0.224</v>
-      </c>
-      <c r="AW25">
-        <v>0.107</v>
       </c>
     </row>
   </sheetData>
